--- a/SOF_TEMPLATE.xlsx
+++ b/SOF_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eun.aasmahri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD046A07-7A34-4DBD-A57D-82DF89AE8866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEC0F25-4FB3-499E-A2B3-B4C0F52918EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -342,7 +342,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="36">
     <border>
       <left/>
       <right/>
@@ -635,17 +635,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -764,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -933,25 +922,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -960,106 +949,23 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1067,11 +973,95 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1287,11 +1277,11 @@
       <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="93"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="79"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1306,11 +1296,11 @@
       <c r="M2" s="9"/>
     </row>
     <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="118" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
-      <c r="C3" s="86"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="83"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1325,9 +1315,9 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="87"/>
-      <c r="B4" s="88"/>
-      <c r="C4" s="89"/>
+      <c r="A4" s="112"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="96"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1342,49 +1332,49 @@
       <c r="M4" s="16"/>
     </row>
     <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="77" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="96" t="s">
+      <c r="B5" s="78"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="95"/>
-      <c r="K5" s="97"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+      <c r="J5" s="78"/>
+      <c r="K5" s="90"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="88"/>
-      <c r="C6" s="89"/>
-      <c r="D6" s="100" t="s">
+      <c r="B6" s="94"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="102"/>
+      <c r="E6" s="94"/>
+      <c r="F6" s="94"/>
+      <c r="G6" s="94"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="92"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="95"/>
-      <c r="C7" s="93"/>
+      <c r="B7" s="78"/>
+      <c r="C7" s="79"/>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1392,120 +1382,120 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="96" t="s">
+      <c r="I7" s="105" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="95"/>
-      <c r="K7" s="97"/>
+      <c r="J7" s="78"/>
+      <c r="K7" s="90"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
     </row>
     <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="106" t="s">
+      <c r="A8" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="85"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="98" t="s">
+      <c r="B8" s="100"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
-      <c r="H8" s="88"/>
-      <c r="I8" s="105" t="s">
+      <c r="E8" s="94"/>
+      <c r="F8" s="94"/>
+      <c r="G8" s="94"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="109" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="88"/>
-      <c r="K8" s="102"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="92"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="107"/>
-      <c r="B9" s="85"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="94" t="s">
+      <c r="A9" s="111"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="108" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="95"/>
-      <c r="F9" s="95"/>
-      <c r="G9" s="95"/>
-      <c r="H9" s="93"/>
-      <c r="I9" s="96" t="s">
+      <c r="E9" s="78"/>
+      <c r="F9" s="78"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="95"/>
-      <c r="K9" s="97"/>
+      <c r="J9" s="78"/>
+      <c r="K9" s="90"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
     <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="87"/>
-      <c r="B10" s="88"/>
-      <c r="C10" s="89"/>
-      <c r="D10" s="98" t="s">
+      <c r="A10" s="112"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="88"/>
-      <c r="F10" s="88"/>
-      <c r="G10" s="88"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="111" t="s">
+      <c r="E10" s="94"/>
+      <c r="F10" s="94"/>
+      <c r="G10" s="94"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="88"/>
-      <c r="K10" s="102"/>
+      <c r="J10" s="94"/>
+      <c r="K10" s="92"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="20"/>
     </row>
     <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="99" t="s">
+      <c r="A11" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="95"/>
-      <c r="C11" s="93"/>
-      <c r="D11" s="94" t="s">
+      <c r="B11" s="78"/>
+      <c r="C11" s="79"/>
+      <c r="D11" s="108" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="95"/>
-      <c r="F11" s="95"/>
-      <c r="G11" s="95"/>
-      <c r="H11" s="93"/>
-      <c r="I11" s="96" t="s">
+      <c r="E11" s="78"/>
+      <c r="F11" s="78"/>
+      <c r="G11" s="78"/>
+      <c r="H11" s="79"/>
+      <c r="I11" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="95"/>
-      <c r="K11" s="97"/>
+      <c r="J11" s="78"/>
+      <c r="K11" s="90"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="108" t="s">
+      <c r="A12" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="85"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="98" t="s">
+      <c r="B12" s="100"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="88"/>
-      <c r="F12" s="88"/>
-      <c r="G12" s="88"/>
-      <c r="H12" s="88"/>
-      <c r="I12" s="111" t="s">
+      <c r="E12" s="94"/>
+      <c r="F12" s="94"/>
+      <c r="G12" s="94"/>
+      <c r="H12" s="94"/>
+      <c r="I12" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="88"/>
-      <c r="K12" s="102"/>
+      <c r="J12" s="94"/>
+      <c r="K12" s="92"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="107"/>
-      <c r="B13" s="85"/>
-      <c r="C13" s="86"/>
+      <c r="A13" s="111"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="83"/>
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
@@ -1521,46 +1511,46 @@
       <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="87"/>
-      <c r="B14" s="88"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="109" t="s">
+      <c r="A14" s="112"/>
+      <c r="B14" s="94"/>
+      <c r="C14" s="96"/>
+      <c r="D14" s="114" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="95"/>
-      <c r="F14" s="95"/>
-      <c r="G14" s="95"/>
-      <c r="H14" s="95"/>
-      <c r="I14" s="95"/>
-      <c r="J14" s="95"/>
-      <c r="K14" s="97"/>
+      <c r="E14" s="78"/>
+      <c r="F14" s="78"/>
+      <c r="G14" s="78"/>
+      <c r="H14" s="78"/>
+      <c r="I14" s="78"/>
+      <c r="J14" s="78"/>
+      <c r="K14" s="90"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
     <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="86"/>
+      <c r="B15" s="83"/>
       <c r="C15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="101"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="88"/>
-      <c r="I15" s="88"/>
-      <c r="J15" s="88"/>
-      <c r="K15" s="102"/>
+      <c r="D15" s="91"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="94"/>
+      <c r="K15" s="92"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
     </row>
     <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="119" t="s">
+      <c r="A16" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="86"/>
+      <c r="B16" s="83"/>
       <c r="C16" s="25" t="s">
         <v>30</v>
       </c>
@@ -1578,47 +1568,47 @@
       <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="99" t="s">
+      <c r="A17" s="77" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="95"/>
-      <c r="C17" s="93"/>
-      <c r="D17" s="100" t="s">
+      <c r="B17" s="78"/>
+      <c r="C17" s="79"/>
+      <c r="D17" s="107" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="82"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="84"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="91" t="s">
+      <c r="A18" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="88"/>
-      <c r="C18" s="89"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="88"/>
-      <c r="F18" s="88"/>
-      <c r="G18" s="88"/>
-      <c r="H18" s="88"/>
-      <c r="I18" s="88"/>
-      <c r="J18" s="88"/>
-      <c r="K18" s="102"/>
+      <c r="B18" s="94"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="94"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="94"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="94"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="92"/>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
     </row>
     <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="104" t="s">
+      <c r="A19" s="98" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="95"/>
+      <c r="B19" s="78"/>
+      <c r="C19" s="78"/>
       <c r="D19" s="29" t="s">
         <v>36</v>
       </c>
@@ -1633,11 +1623,11 @@
       <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="91" t="s">
+      <c r="A20" s="95" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="88"/>
-      <c r="C20" s="89"/>
+      <c r="B20" s="94"/>
+      <c r="C20" s="96"/>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -1650,11 +1640,11 @@
       <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="95"/>
-      <c r="C21" s="93"/>
+      <c r="B21" s="78"/>
+      <c r="C21" s="79"/>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -1667,11 +1657,11 @@
       <c r="M21" s="24"/>
     </row>
     <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="91" t="s">
+      <c r="A22" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="88"/>
-      <c r="C22" s="89"/>
+      <c r="B22" s="94"/>
+      <c r="C22" s="96"/>
       <c r="D22" s="33"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
@@ -1684,11 +1674,11 @@
       <c r="M22" s="18"/>
     </row>
     <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="104" t="s">
+      <c r="A23" s="98" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="95"/>
-      <c r="C23" s="95"/>
+      <c r="B23" s="78"/>
+      <c r="C23" s="78"/>
       <c r="D23" s="35"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1701,11 +1691,11 @@
       <c r="M23" s="24"/>
     </row>
     <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="91" t="s">
+      <c r="A24" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="88"/>
-      <c r="C24" s="89"/>
+      <c r="B24" s="94"/>
+      <c r="C24" s="96"/>
       <c r="D24" s="30"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1719,11 +1709,11 @@
       <c r="N24" s="24"/>
     </row>
     <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="104" t="s">
+      <c r="A25" s="98" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="95"/>
-      <c r="C25" s="95"/>
+      <c r="B25" s="78"/>
+      <c r="C25" s="78"/>
       <c r="D25" s="37"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -1737,11 +1727,11 @@
       <c r="N25" s="24"/>
     </row>
     <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="91" t="s">
+      <c r="A26" s="95" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="88"/>
-      <c r="C26" s="89"/>
+      <c r="B26" s="94"/>
+      <c r="C26" s="96"/>
       <c r="D26" s="37"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
@@ -1755,37 +1745,37 @@
       <c r="N26" s="24"/>
     </row>
     <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="117" t="s">
+      <c r="A27" s="80" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="77" t="s">
+      <c r="B27" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="77" t="s">
+      <c r="C27" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="78"/>
-      <c r="E27" s="77" t="s">
+      <c r="D27" s="88"/>
+      <c r="E27" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="78"/>
+      <c r="F27" s="88"/>
       <c r="G27" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="92" t="s">
+      <c r="H27" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="I27" s="93"/>
-      <c r="J27" s="121" t="s">
+      <c r="I27" s="79"/>
+      <c r="J27" s="89" t="s">
         <v>50</v>
       </c>
-      <c r="K27" s="97"/>
+      <c r="K27" s="90"/>
       <c r="L27" s="40"/>
       <c r="M27" s="40"/>
     </row>
     <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="118"/>
-      <c r="B28" s="83"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="117"/>
       <c r="C28" s="38" t="s">
         <v>51</v>
       </c>
@@ -1801,12 +1791,12 @@
       <c r="G28" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="90" t="s">
+      <c r="H28" s="119" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="89"/>
-      <c r="J28" s="101"/>
-      <c r="K28" s="102"/>
+      <c r="I28" s="96"/>
+      <c r="J28" s="91"/>
+      <c r="K28" s="92"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
     </row>
@@ -1917,8 +1907,8 @@
       <c r="G34" s="23"/>
       <c r="H34" s="51"/>
       <c r="I34" s="11"/>
-      <c r="J34" s="81"/>
-      <c r="K34" s="82"/>
+      <c r="J34" s="122"/>
+      <c r="K34" s="121"/>
       <c r="L34" s="40"/>
       <c r="M34" s="40"/>
     </row>
@@ -2052,8 +2042,8 @@
       <c r="G43" s="23"/>
       <c r="H43" s="51"/>
       <c r="I43" s="11"/>
-      <c r="J43" s="81"/>
-      <c r="K43" s="82"/>
+      <c r="J43" s="122"/>
+      <c r="K43" s="121"/>
       <c r="L43" s="40"/>
       <c r="M43" s="40"/>
     </row>
@@ -2308,10 +2298,10 @@
       <c r="I59" s="11"/>
       <c r="J59" s="61"/>
       <c r="K59" s="53"/>
-      <c r="N59" s="113"/>
-      <c r="O59" s="85"/>
-      <c r="P59" s="85"/>
-      <c r="Q59" s="85"/>
+      <c r="N59" s="101"/>
+      <c r="O59" s="100"/>
+      <c r="P59" s="100"/>
+      <c r="Q59" s="100"/>
     </row>
     <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="62" t="s">
@@ -2414,40 +2404,40 @@
       <c r="N66" s="22"/>
     </row>
     <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="79" t="s">
+      <c r="A67" s="116" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="80"/>
-      <c r="C67" s="80"/>
-      <c r="D67" s="120"/>
-      <c r="E67" s="80"/>
-      <c r="F67" s="80"/>
-      <c r="G67" s="80"/>
-      <c r="H67" s="80"/>
-      <c r="I67" s="80"/>
-      <c r="J67" s="115" t="s">
+      <c r="B67" s="86"/>
+      <c r="C67" s="86"/>
+      <c r="D67" s="85"/>
+      <c r="E67" s="86"/>
+      <c r="F67" s="86"/>
+      <c r="G67" s="86"/>
+      <c r="H67" s="86"/>
+      <c r="I67" s="86"/>
+      <c r="J67" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="K67" s="116"/>
+      <c r="K67" s="104"/>
       <c r="L67" s="69"/>
       <c r="M67" s="69"/>
     </row>
     <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="112" t="s">
+      <c r="A68" s="99" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="85"/>
-      <c r="C68" s="85"/>
-      <c r="D68" s="110"/>
-      <c r="E68" s="85"/>
-      <c r="F68" s="85"/>
-      <c r="G68" s="85"/>
-      <c r="H68" s="85"/>
-      <c r="I68" s="85"/>
-      <c r="J68" s="103" t="s">
+      <c r="B68" s="100"/>
+      <c r="C68" s="100"/>
+      <c r="D68" s="115"/>
+      <c r="E68" s="100"/>
+      <c r="F68" s="100"/>
+      <c r="G68" s="100"/>
+      <c r="H68" s="100"/>
+      <c r="I68" s="100"/>
+      <c r="J68" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="K68" s="82"/>
+      <c r="K68" s="84"/>
       <c r="L68" s="71"/>
       <c r="M68" s="71"/>
     </row>
@@ -2557,46 +2547,7 @@
     <row r="76" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="D67:I67"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="J27:K28"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="N59:Q59"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A8:C10"/>
-    <mergeCell ref="A12:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D14:K15"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="D68:I68"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="B27:B28"/>
+  <mergeCells count="49">
     <mergeCell ref="A3:C4"/>
     <mergeCell ref="H28:I28"/>
     <mergeCell ref="A24:C24"/>
@@ -2609,6 +2560,43 @@
     <mergeCell ref="D17:K18"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A8:C10"/>
+    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D14:K15"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="D68:I68"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D67:I67"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A5:C5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15763888888888899" right="0.15763888888888899" top="0.27569444444444402" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/SOF_TEMPLATE.xlsx
+++ b/SOF_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eun.aasmahri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFEC0F25-4FB3-499E-A2B3-B4C0F52918EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C3F5C6-5EB3-453C-AE19-9254E75D859A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -961,11 +961,92 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -973,95 +1054,14 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1277,11 +1277,11 @@
       <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="77" t="s">
+      <c r="A2" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="78"/>
-      <c r="C2" s="79"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="88"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1296,11 +1296,11 @@
       <c r="M2" s="9"/>
     </row>
     <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="118" t="s">
+      <c r="A3" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3" s="83"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="81"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1315,9 +1315,9 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="112"/>
-      <c r="B4" s="94"/>
-      <c r="C4" s="96"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1332,49 +1332,49 @@
       <c r="M4" s="16"/>
     </row>
     <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="77" t="s">
+      <c r="A5" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="78"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="105" t="s">
+      <c r="B5" s="90"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="91" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
-      <c r="J5" s="78"/>
-      <c r="K5" s="90"/>
+      <c r="E5" s="90"/>
+      <c r="F5" s="90"/>
+      <c r="G5" s="90"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="90"/>
+      <c r="J5" s="90"/>
+      <c r="K5" s="92"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="118" t="s">
+      <c r="A6" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="94"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="107" t="s">
+      <c r="B6" s="83"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="95" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="94"/>
-      <c r="F6" s="94"/>
-      <c r="G6" s="94"/>
-      <c r="H6" s="94"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="94"/>
-      <c r="K6" s="92"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+      <c r="K6" s="98"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="77" t="s">
+      <c r="A7" s="94" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="79"/>
+      <c r="B7" s="90"/>
+      <c r="C7" s="88"/>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1382,120 +1382,120 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="105" t="s">
+      <c r="I7" s="91" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="78"/>
-      <c r="K7" s="90"/>
+      <c r="J7" s="90"/>
+      <c r="K7" s="92"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
     </row>
     <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="100"/>
-      <c r="C8" s="83"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="81"/>
       <c r="D8" s="93" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="94"/>
-      <c r="F8" s="94"/>
-      <c r="G8" s="94"/>
-      <c r="H8" s="94"/>
-      <c r="I8" s="109" t="s">
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="94"/>
-      <c r="K8" s="92"/>
+      <c r="J8" s="83"/>
+      <c r="K8" s="98"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="111"/>
-      <c r="B9" s="100"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="108" t="s">
+      <c r="A9" s="102"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="89" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="78"/>
-      <c r="F9" s="78"/>
-      <c r="G9" s="78"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="105" t="s">
+      <c r="E9" s="90"/>
+      <c r="F9" s="90"/>
+      <c r="G9" s="90"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="91" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="78"/>
-      <c r="K9" s="90"/>
+      <c r="J9" s="90"/>
+      <c r="K9" s="92"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
     <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="112"/>
-      <c r="B10" s="94"/>
-      <c r="C10" s="96"/>
+      <c r="A10" s="82"/>
+      <c r="B10" s="83"/>
+      <c r="C10" s="84"/>
       <c r="D10" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="94"/>
-      <c r="F10" s="94"/>
-      <c r="G10" s="94"/>
-      <c r="H10" s="94"/>
-      <c r="I10" s="97" t="s">
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="122" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="94"/>
-      <c r="K10" s="92"/>
+      <c r="J10" s="83"/>
+      <c r="K10" s="98"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="20"/>
     </row>
     <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="94" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="78"/>
-      <c r="C11" s="79"/>
-      <c r="D11" s="108" t="s">
+      <c r="B11" s="90"/>
+      <c r="C11" s="88"/>
+      <c r="D11" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="78"/>
-      <c r="F11" s="78"/>
-      <c r="G11" s="78"/>
-      <c r="H11" s="79"/>
-      <c r="I11" s="105" t="s">
+      <c r="E11" s="90"/>
+      <c r="F11" s="90"/>
+      <c r="G11" s="90"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="91" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="78"/>
-      <c r="K11" s="90"/>
+      <c r="J11" s="90"/>
+      <c r="K11" s="92"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="113" t="s">
+      <c r="A12" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="83"/>
+      <c r="B12" s="80"/>
+      <c r="C12" s="81"/>
       <c r="D12" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="94"/>
-      <c r="F12" s="94"/>
-      <c r="G12" s="94"/>
-      <c r="H12" s="94"/>
-      <c r="I12" s="97" t="s">
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="94"/>
-      <c r="K12" s="92"/>
+      <c r="J12" s="83"/>
+      <c r="K12" s="98"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="111"/>
-      <c r="B13" s="100"/>
-      <c r="C13" s="83"/>
+      <c r="A13" s="102"/>
+      <c r="B13" s="80"/>
+      <c r="C13" s="81"/>
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
@@ -1511,46 +1511,46 @@
       <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="112"/>
-      <c r="B14" s="94"/>
-      <c r="C14" s="96"/>
-      <c r="D14" s="114" t="s">
+      <c r="A14" s="82"/>
+      <c r="B14" s="83"/>
+      <c r="C14" s="84"/>
+      <c r="D14" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="78"/>
-      <c r="F14" s="78"/>
-      <c r="G14" s="78"/>
-      <c r="H14" s="78"/>
-      <c r="I14" s="78"/>
-      <c r="J14" s="78"/>
-      <c r="K14" s="90"/>
+      <c r="E14" s="90"/>
+      <c r="F14" s="90"/>
+      <c r="G14" s="90"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="90"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="92"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
     <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="102" t="s">
+      <c r="A15" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="83"/>
+      <c r="B15" s="81"/>
       <c r="C15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="91"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="94"/>
-      <c r="K15" s="92"/>
+      <c r="D15" s="97"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="83"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="83"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="83"/>
+      <c r="K15" s="98"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
     </row>
     <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="82" t="s">
+      <c r="A16" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="83"/>
+      <c r="B16" s="81"/>
       <c r="C16" s="25" t="s">
         <v>30</v>
       </c>
@@ -1568,47 +1568,47 @@
       <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="77" t="s">
+      <c r="A17" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="78"/>
-      <c r="C17" s="79"/>
-      <c r="D17" s="107" t="s">
+      <c r="B17" s="90"/>
+      <c r="C17" s="88"/>
+      <c r="D17" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="100"/>
-      <c r="F17" s="100"/>
-      <c r="G17" s="100"/>
-      <c r="H17" s="100"/>
-      <c r="I17" s="100"/>
-      <c r="J17" s="100"/>
-      <c r="K17" s="84"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="80"/>
+      <c r="H17" s="80"/>
+      <c r="I17" s="80"/>
+      <c r="J17" s="80"/>
+      <c r="K17" s="96"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="95" t="s">
+      <c r="A18" s="86" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="94"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="94"/>
-      <c r="F18" s="94"/>
-      <c r="G18" s="94"/>
-      <c r="H18" s="94"/>
-      <c r="I18" s="94"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="92"/>
+      <c r="B18" s="83"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="83"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="83"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="83"/>
+      <c r="K18" s="98"/>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
     </row>
     <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="98" t="s">
+      <c r="A19" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="78"/>
-      <c r="C19" s="78"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
       <c r="D19" s="29" t="s">
         <v>36</v>
       </c>
@@ -1623,11 +1623,11 @@
       <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="95" t="s">
+      <c r="A20" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="94"/>
-      <c r="C20" s="96"/>
+      <c r="B20" s="83"/>
+      <c r="C20" s="84"/>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -1640,11 +1640,11 @@
       <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="77" t="s">
+      <c r="A21" s="94" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="78"/>
-      <c r="C21" s="79"/>
+      <c r="B21" s="90"/>
+      <c r="C21" s="88"/>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -1657,11 +1657,11 @@
       <c r="M21" s="24"/>
     </row>
     <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="95" t="s">
+      <c r="A22" s="86" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="94"/>
-      <c r="C22" s="96"/>
+      <c r="B22" s="83"/>
+      <c r="C22" s="84"/>
       <c r="D22" s="33"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
@@ -1674,11 +1674,11 @@
       <c r="M22" s="18"/>
     </row>
     <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="98" t="s">
+      <c r="A23" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="78"/>
-      <c r="C23" s="78"/>
+      <c r="B23" s="90"/>
+      <c r="C23" s="90"/>
       <c r="D23" s="35"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1691,11 +1691,11 @@
       <c r="M23" s="24"/>
     </row>
     <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="86" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="94"/>
-      <c r="C24" s="96"/>
+      <c r="B24" s="83"/>
+      <c r="C24" s="84"/>
       <c r="D24" s="30"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1709,11 +1709,11 @@
       <c r="N24" s="24"/>
     </row>
     <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="98" t="s">
+      <c r="A25" s="99" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="78"/>
-      <c r="C25" s="78"/>
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
       <c r="D25" s="37"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -1727,11 +1727,11 @@
       <c r="N25" s="24"/>
     </row>
     <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="95" t="s">
+      <c r="A26" s="86" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="94"/>
-      <c r="C26" s="96"/>
+      <c r="B26" s="83"/>
+      <c r="C26" s="84"/>
       <c r="D26" s="37"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
@@ -1745,37 +1745,37 @@
       <c r="N26" s="24"/>
     </row>
     <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="80" t="s">
+      <c r="A27" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="87" t="s">
+      <c r="B27" s="112" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="87" t="s">
+      <c r="C27" s="112" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="88"/>
-      <c r="E27" s="87" t="s">
+      <c r="D27" s="113"/>
+      <c r="E27" s="112" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="88"/>
+      <c r="F27" s="113"/>
       <c r="G27" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="120" t="s">
+      <c r="H27" s="87" t="s">
         <v>49</v>
       </c>
-      <c r="I27" s="79"/>
-      <c r="J27" s="89" t="s">
+      <c r="I27" s="88"/>
+      <c r="J27" s="121" t="s">
         <v>50</v>
       </c>
-      <c r="K27" s="90"/>
+      <c r="K27" s="92"/>
       <c r="L27" s="40"/>
       <c r="M27" s="40"/>
     </row>
     <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="81"/>
-      <c r="B28" s="117"/>
+      <c r="A28" s="118"/>
+      <c r="B28" s="116"/>
       <c r="C28" s="38" t="s">
         <v>51</v>
       </c>
@@ -1791,12 +1791,12 @@
       <c r="G28" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="119" t="s">
+      <c r="H28" s="85" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="96"/>
-      <c r="J28" s="91"/>
-      <c r="K28" s="92"/>
+      <c r="I28" s="84"/>
+      <c r="J28" s="97"/>
+      <c r="K28" s="98"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
     </row>
@@ -1907,8 +1907,8 @@
       <c r="G34" s="23"/>
       <c r="H34" s="51"/>
       <c r="I34" s="11"/>
-      <c r="J34" s="122"/>
-      <c r="K34" s="121"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="46"/>
       <c r="L34" s="40"/>
       <c r="M34" s="40"/>
     </row>
@@ -2042,8 +2042,8 @@
       <c r="G43" s="23"/>
       <c r="H43" s="51"/>
       <c r="I43" s="11"/>
-      <c r="J43" s="122"/>
-      <c r="K43" s="121"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="77"/>
       <c r="L43" s="40"/>
       <c r="M43" s="40"/>
     </row>
@@ -2298,10 +2298,10 @@
       <c r="I59" s="11"/>
       <c r="J59" s="61"/>
       <c r="K59" s="53"/>
-      <c r="N59" s="101"/>
-      <c r="O59" s="100"/>
-      <c r="P59" s="100"/>
-      <c r="Q59" s="100"/>
+      <c r="N59" s="106"/>
+      <c r="O59" s="80"/>
+      <c r="P59" s="80"/>
+      <c r="Q59" s="80"/>
     </row>
     <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="62" t="s">
@@ -2404,40 +2404,40 @@
       <c r="N66" s="22"/>
     </row>
     <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="116" t="s">
+      <c r="A67" s="114" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="86"/>
-      <c r="C67" s="86"/>
-      <c r="D67" s="85"/>
-      <c r="E67" s="86"/>
-      <c r="F67" s="86"/>
-      <c r="G67" s="86"/>
-      <c r="H67" s="86"/>
-      <c r="I67" s="86"/>
-      <c r="J67" s="103" t="s">
+      <c r="B67" s="115"/>
+      <c r="C67" s="115"/>
+      <c r="D67" s="120"/>
+      <c r="E67" s="115"/>
+      <c r="F67" s="115"/>
+      <c r="G67" s="115"/>
+      <c r="H67" s="115"/>
+      <c r="I67" s="115"/>
+      <c r="J67" s="108" t="s">
         <v>70</v>
       </c>
-      <c r="K67" s="104"/>
+      <c r="K67" s="109"/>
       <c r="L67" s="69"/>
       <c r="M67" s="69"/>
     </row>
     <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="99" t="s">
+      <c r="A68" s="105" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="100"/>
-      <c r="C68" s="100"/>
-      <c r="D68" s="115"/>
-      <c r="E68" s="100"/>
-      <c r="F68" s="100"/>
-      <c r="G68" s="100"/>
-      <c r="H68" s="100"/>
-      <c r="I68" s="100"/>
-      <c r="J68" s="106" t="s">
+      <c r="B68" s="80"/>
+      <c r="C68" s="80"/>
+      <c r="D68" s="111"/>
+      <c r="E68" s="80"/>
+      <c r="F68" s="80"/>
+      <c r="G68" s="80"/>
+      <c r="H68" s="80"/>
+      <c r="I68" s="80"/>
+      <c r="J68" s="110" t="s">
         <v>72</v>
       </c>
-      <c r="K68" s="84"/>
+      <c r="K68" s="96"/>
       <c r="L68" s="71"/>
       <c r="M68" s="71"/>
     </row>
@@ -2548,6 +2548,39 @@
     <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D67:I67"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="D68:I68"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="A8:C10"/>
+    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D14:K15"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A3:C4"/>
     <mergeCell ref="H28:I28"/>
     <mergeCell ref="A24:C24"/>
@@ -2564,39 +2597,6 @@
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="D11:H11"/>
     <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A8:C10"/>
-    <mergeCell ref="A12:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D14:K15"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="N59:Q59"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="D68:I68"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D67:I67"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="J27:K28"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A5:C5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15763888888888899" right="0.15763888888888899" top="0.27569444444444402" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/SOF_TEMPLATE.xlsx
+++ b/SOF_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eun.aasmahri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14C3F5C6-5EB3-453C-AE19-9254E75D859A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F2FFD6-100F-4F12-9AAC-AE834F531C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -753,7 +753,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="123">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -965,88 +965,11 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1054,14 +977,97 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1277,11 +1283,11 @@
       <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="79" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="90"/>
-      <c r="C2" s="88"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="81"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1296,11 +1302,11 @@
       <c r="M2" s="9"/>
     </row>
     <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="79" t="s">
+      <c r="A3" s="117" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="80"/>
-      <c r="C3" s="81"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="85"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1315,9 +1321,9 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
+      <c r="A4" s="114"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="93"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1332,49 +1338,49 @@
       <c r="M4" s="16"/>
     </row>
     <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="90"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="91" t="s">
+      <c r="B5" s="80"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="103" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="90"/>
-      <c r="F5" s="90"/>
-      <c r="G5" s="90"/>
-      <c r="H5" s="90"/>
-      <c r="I5" s="90"/>
-      <c r="J5" s="90"/>
-      <c r="K5" s="92"/>
+      <c r="E5" s="80"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="80"/>
+      <c r="H5" s="80"/>
+      <c r="I5" s="80"/>
+      <c r="J5" s="80"/>
+      <c r="K5" s="104"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="83"/>
-      <c r="C6" s="84"/>
-      <c r="D6" s="95" t="s">
+      <c r="B6" s="91"/>
+      <c r="C6" s="93"/>
+      <c r="D6" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="98"/>
+      <c r="E6" s="91"/>
+      <c r="F6" s="91"/>
+      <c r="G6" s="91"/>
+      <c r="H6" s="91"/>
+      <c r="I6" s="91"/>
+      <c r="J6" s="91"/>
+      <c r="K6" s="95"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="94" t="s">
+      <c r="A7" s="79" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="90"/>
-      <c r="C7" s="88"/>
+      <c r="B7" s="80"/>
+      <c r="C7" s="81"/>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1382,120 +1388,120 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="91" t="s">
+      <c r="I7" s="103" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="90"/>
-      <c r="K7" s="92"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="104"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
     </row>
     <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="101" t="s">
+      <c r="A8" s="112" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="93" t="s">
+      <c r="B8" s="98"/>
+      <c r="C8" s="85"/>
+      <c r="D8" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="100" t="s">
+      <c r="E8" s="91"/>
+      <c r="F8" s="91"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="91"/>
+      <c r="I8" s="122" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="83"/>
-      <c r="K8" s="98"/>
+      <c r="J8" s="91"/>
+      <c r="K8" s="95"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="102"/>
-      <c r="B9" s="80"/>
-      <c r="C9" s="81"/>
-      <c r="D9" s="89" t="s">
+      <c r="A9" s="113"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="85"/>
+      <c r="D9" s="120" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="90"/>
-      <c r="F9" s="90"/>
-      <c r="G9" s="90"/>
-      <c r="H9" s="88"/>
-      <c r="I9" s="91" t="s">
+      <c r="E9" s="80"/>
+      <c r="F9" s="80"/>
+      <c r="G9" s="80"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="90"/>
-      <c r="K9" s="92"/>
+      <c r="J9" s="80"/>
+      <c r="K9" s="104"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
     <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="82"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="84"/>
-      <c r="D10" s="93" t="s">
+      <c r="A10" s="114"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="93"/>
+      <c r="D10" s="90" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="122" t="s">
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91"/>
+      <c r="H10" s="91"/>
+      <c r="I10" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="83"/>
-      <c r="K10" s="98"/>
+      <c r="J10" s="91"/>
+      <c r="K10" s="95"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="20"/>
     </row>
     <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="94" t="s">
+      <c r="A11" s="79" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="90"/>
-      <c r="C11" s="88"/>
-      <c r="D11" s="89" t="s">
+      <c r="B11" s="80"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="90"/>
-      <c r="F11" s="90"/>
-      <c r="G11" s="90"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="91" t="s">
+      <c r="E11" s="80"/>
+      <c r="F11" s="80"/>
+      <c r="G11" s="80"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="90"/>
-      <c r="K11" s="92"/>
+      <c r="J11" s="80"/>
+      <c r="K11" s="104"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="103" t="s">
+      <c r="A12" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="80"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="93" t="s">
+      <c r="B12" s="98"/>
+      <c r="C12" s="85"/>
+      <c r="D12" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="122" t="s">
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91"/>
+      <c r="H12" s="91"/>
+      <c r="I12" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="83"/>
-      <c r="K12" s="98"/>
+      <c r="J12" s="91"/>
+      <c r="K12" s="95"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="102"/>
-      <c r="B13" s="80"/>
-      <c r="C13" s="81"/>
+      <c r="A13" s="113"/>
+      <c r="B13" s="98"/>
+      <c r="C13" s="85"/>
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
@@ -1511,46 +1517,46 @@
       <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="82"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="104" t="s">
+      <c r="A14" s="114"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="93"/>
+      <c r="D14" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="90"/>
-      <c r="J14" s="90"/>
-      <c r="K14" s="92"/>
+      <c r="E14" s="80"/>
+      <c r="F14" s="80"/>
+      <c r="G14" s="80"/>
+      <c r="H14" s="80"/>
+      <c r="I14" s="80"/>
+      <c r="J14" s="80"/>
+      <c r="K14" s="104"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
     <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="107" t="s">
+      <c r="A15" s="100" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="81"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="97"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="98"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="91"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="91"/>
+      <c r="H15" s="91"/>
+      <c r="I15" s="91"/>
+      <c r="J15" s="91"/>
+      <c r="K15" s="95"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
     </row>
     <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="119" t="s">
+      <c r="A16" s="84" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="81"/>
+      <c r="B16" s="85"/>
       <c r="C16" s="25" t="s">
         <v>30</v>
       </c>
@@ -1568,47 +1574,47 @@
       <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="94" t="s">
+      <c r="A17" s="79" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="90"/>
-      <c r="C17" s="88"/>
-      <c r="D17" s="95" t="s">
+      <c r="B17" s="80"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="121" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="80"/>
-      <c r="H17" s="80"/>
-      <c r="I17" s="80"/>
-      <c r="J17" s="80"/>
-      <c r="K17" s="96"/>
+      <c r="E17" s="98"/>
+      <c r="F17" s="98"/>
+      <c r="G17" s="98"/>
+      <c r="H17" s="98"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="98"/>
+      <c r="K17" s="106"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="86" t="s">
+      <c r="A18" s="92" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="83"/>
-      <c r="C18" s="84"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="83"/>
-      <c r="K18" s="98"/>
+      <c r="B18" s="91"/>
+      <c r="C18" s="93"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="91"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="91"/>
+      <c r="H18" s="91"/>
+      <c r="I18" s="91"/>
+      <c r="J18" s="91"/>
+      <c r="K18" s="95"/>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
     </row>
     <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="99" t="s">
+      <c r="A19" s="96" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
+      <c r="B19" s="80"/>
+      <c r="C19" s="80"/>
       <c r="D19" s="29" t="s">
         <v>36</v>
       </c>
@@ -1623,11 +1629,11 @@
       <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="92" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="83"/>
-      <c r="C20" s="84"/>
+      <c r="B20" s="91"/>
+      <c r="C20" s="93"/>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -1640,11 +1646,11 @@
       <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="94" t="s">
+      <c r="A21" s="79" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="90"/>
-      <c r="C21" s="88"/>
+      <c r="B21" s="80"/>
+      <c r="C21" s="81"/>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -1657,11 +1663,11 @@
       <c r="M21" s="24"/>
     </row>
     <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="92" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="83"/>
-      <c r="C22" s="84"/>
+      <c r="B22" s="91"/>
+      <c r="C22" s="93"/>
       <c r="D22" s="33"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
@@ -1674,11 +1680,11 @@
       <c r="M22" s="18"/>
     </row>
     <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="99" t="s">
+      <c r="A23" s="96" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="90"/>
-      <c r="C23" s="90"/>
+      <c r="B23" s="80"/>
+      <c r="C23" s="80"/>
       <c r="D23" s="35"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1691,11 +1697,11 @@
       <c r="M23" s="24"/>
     </row>
     <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="92" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="83"/>
-      <c r="C24" s="84"/>
+      <c r="B24" s="91"/>
+      <c r="C24" s="93"/>
       <c r="D24" s="30"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1709,11 +1715,11 @@
       <c r="N24" s="24"/>
     </row>
     <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="99" t="s">
+      <c r="A25" s="96" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="90"/>
-      <c r="C25" s="90"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
       <c r="D25" s="37"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -1727,11 +1733,11 @@
       <c r="N25" s="24"/>
     </row>
     <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="86" t="s">
+      <c r="A26" s="92" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="83"/>
-      <c r="C26" s="84"/>
+      <c r="B26" s="91"/>
+      <c r="C26" s="93"/>
       <c r="D26" s="37"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
@@ -1745,37 +1751,37 @@
       <c r="N26" s="24"/>
     </row>
     <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="117" t="s">
+      <c r="A27" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="112" t="s">
+      <c r="B27" s="88" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="112" t="s">
+      <c r="C27" s="88" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="113"/>
-      <c r="E27" s="112" t="s">
+      <c r="D27" s="89"/>
+      <c r="E27" s="88" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="113"/>
+      <c r="F27" s="89"/>
       <c r="G27" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="87" t="s">
+      <c r="H27" s="119" t="s">
         <v>49</v>
       </c>
-      <c r="I27" s="88"/>
-      <c r="J27" s="121" t="s">
+      <c r="I27" s="81"/>
+      <c r="J27" s="110" t="s">
         <v>50</v>
       </c>
-      <c r="K27" s="92"/>
+      <c r="K27" s="104"/>
       <c r="L27" s="40"/>
       <c r="M27" s="40"/>
     </row>
     <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="118"/>
-      <c r="B28" s="116"/>
+      <c r="A28" s="83"/>
+      <c r="B28" s="109"/>
       <c r="C28" s="38" t="s">
         <v>51</v>
       </c>
@@ -1791,12 +1797,12 @@
       <c r="G28" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="85" t="s">
+      <c r="H28" s="118" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="84"/>
-      <c r="J28" s="97"/>
-      <c r="K28" s="98"/>
+      <c r="I28" s="93"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="95"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
     </row>
@@ -1907,8 +1913,8 @@
       <c r="G34" s="23"/>
       <c r="H34" s="51"/>
       <c r="I34" s="11"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="46"/>
+      <c r="J34" s="123"/>
+      <c r="K34" s="124"/>
       <c r="L34" s="40"/>
       <c r="M34" s="40"/>
     </row>
@@ -2298,10 +2304,10 @@
       <c r="I59" s="11"/>
       <c r="J59" s="61"/>
       <c r="K59" s="53"/>
-      <c r="N59" s="106"/>
-      <c r="O59" s="80"/>
-      <c r="P59" s="80"/>
-      <c r="Q59" s="80"/>
+      <c r="N59" s="99"/>
+      <c r="O59" s="98"/>
+      <c r="P59" s="98"/>
+      <c r="Q59" s="98"/>
     </row>
     <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="62" t="s">
@@ -2404,40 +2410,40 @@
       <c r="N66" s="22"/>
     </row>
     <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="114" t="s">
+      <c r="A67" s="108" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="115"/>
-      <c r="C67" s="115"/>
-      <c r="D67" s="120"/>
-      <c r="E67" s="115"/>
-      <c r="F67" s="115"/>
-      <c r="G67" s="115"/>
-      <c r="H67" s="115"/>
-      <c r="I67" s="115"/>
-      <c r="J67" s="108" t="s">
+      <c r="B67" s="87"/>
+      <c r="C67" s="87"/>
+      <c r="D67" s="86"/>
+      <c r="E67" s="87"/>
+      <c r="F67" s="87"/>
+      <c r="G67" s="87"/>
+      <c r="H67" s="87"/>
+      <c r="I67" s="87"/>
+      <c r="J67" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="K67" s="109"/>
+      <c r="K67" s="102"/>
       <c r="L67" s="69"/>
       <c r="M67" s="69"/>
     </row>
     <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="105" t="s">
+      <c r="A68" s="97" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="80"/>
-      <c r="C68" s="80"/>
-      <c r="D68" s="111"/>
-      <c r="E68" s="80"/>
-      <c r="F68" s="80"/>
-      <c r="G68" s="80"/>
-      <c r="H68" s="80"/>
-      <c r="I68" s="80"/>
-      <c r="J68" s="110" t="s">
+      <c r="B68" s="98"/>
+      <c r="C68" s="98"/>
+      <c r="D68" s="107"/>
+      <c r="E68" s="98"/>
+      <c r="F68" s="98"/>
+      <c r="G68" s="98"/>
+      <c r="H68" s="98"/>
+      <c r="I68" s="98"/>
+      <c r="J68" s="105" t="s">
         <v>72</v>
       </c>
-      <c r="K68" s="96"/>
+      <c r="K68" s="106"/>
       <c r="L68" s="71"/>
       <c r="M68" s="71"/>
     </row>
@@ -2547,21 +2553,25 @@
     <row r="76" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="D67:I67"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="D10:H10"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="I12:K12"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="I10:K10"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A5:C5"/>
+  <mergeCells count="50">
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="J34:K34"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D17:K18"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D11:H11"/>
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="N59:Q59"/>
     <mergeCell ref="A15:B15"/>
@@ -2578,25 +2588,22 @@
     <mergeCell ref="A8:C10"/>
     <mergeCell ref="A12:C14"/>
     <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="D67:I67"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="D10:H10"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="I12:K12"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A5:C5"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D14:K15"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D17:K18"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="I8:K8"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15763888888888899" right="0.15763888888888899" top="0.27569444444444402" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/SOF_TEMPLATE.xlsx
+++ b/SOF_TEMPLATE.xlsx
@@ -16,11 +16,24 @@
     <sheet name="SOF (3)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SOF (3)'!$A$1:$K$75</definedName>
     <definedName name="Texte4" localSheetId="0">'SOF (3)'!$N$16</definedName>
     <definedName name="Texte7" localSheetId="0">'SOF (3)'!$O$20</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'SOF (3)'!$A$1:$K$75</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -965,11 +978,88 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -977,97 +1067,20 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1250,23 +1263,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.4609375" defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="5.85546875" customWidth="1"/>
-    <col min="4" max="4" width="6.5703125" customWidth="1"/>
-    <col min="5" max="6" width="6" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" customWidth="1"/>
-    <col min="8" max="8" width="12.28515625" customWidth="1"/>
-    <col min="9" max="9" width="1.5703125" customWidth="1"/>
-    <col min="10" max="10" width="24.5703125" customWidth="1"/>
-    <col min="11" max="11" width="7.5703125" customWidth="1"/>
-    <col min="12" max="12" width="1" customWidth="1"/>
-    <col min="13" max="13" width="4.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9.84375" customWidth="1"/>
+    <col min="2" max="2" width="12.9453125" customWidth="1"/>
+    <col min="3" max="3" width="5.796875" customWidth="1"/>
+    <col min="4" max="4" width="6.60546875" customWidth="1"/>
+    <col min="5" max="6" width="5.93359375" customWidth="1"/>
+    <col min="7" max="7" width="5.52734375" customWidth="1"/>
+    <col min="8" max="8" width="12.26953125" customWidth="1"/>
+    <col min="9" max="9" width="1.6171875" customWidth="1"/>
+    <col min="10" max="10" width="24.54296875" customWidth="1"/>
+    <col min="11" max="11" width="7.55078125" customWidth="1"/>
+    <col min="12" max="12" width="0.94140625" customWidth="1"/>
+    <col min="13" max="13" width="4.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="75.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="75.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1282,12 +1295,12 @@
       <c r="M1" s="4"/>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="79" t="s">
+    <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="96" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="81"/>
+      <c r="B2" s="92"/>
+      <c r="C2" s="90"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1301,12 +1314,12 @@
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
     </row>
-    <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="117" t="s">
+    <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A3" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="98"/>
-      <c r="C3" s="85"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="86"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1320,10 +1333,10 @@
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
     </row>
-    <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="114"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="93"/>
+    <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A4" s="87"/>
+      <c r="B4" s="80"/>
+      <c r="C4" s="83"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1337,50 +1350,50 @@
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
     </row>
-    <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="79" t="s">
+    <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="103" t="s">
+      <c r="B5" s="92"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="80"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="80"/>
-      <c r="H5" s="80"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="104"/>
+      <c r="E5" s="92"/>
+      <c r="F5" s="92"/>
+      <c r="G5" s="92"/>
+      <c r="H5" s="92"/>
+      <c r="I5" s="92"/>
+      <c r="J5" s="92"/>
+      <c r="K5" s="94"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
     </row>
-    <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="117" t="s">
+    <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A6" s="84" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="91"/>
-      <c r="C6" s="93"/>
-      <c r="D6" s="121" t="s">
+      <c r="B6" s="80"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="97" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="91"/>
-      <c r="F6" s="91"/>
-      <c r="G6" s="91"/>
-      <c r="H6" s="91"/>
-      <c r="I6" s="91"/>
-      <c r="J6" s="91"/>
-      <c r="K6" s="95"/>
+      <c r="E6" s="80"/>
+      <c r="F6" s="80"/>
+      <c r="G6" s="80"/>
+      <c r="H6" s="80"/>
+      <c r="I6" s="80"/>
+      <c r="J6" s="80"/>
+      <c r="K6" s="81"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
-    <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="79" t="s">
+    <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A7" s="96" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="80"/>
-      <c r="C7" s="81"/>
+      <c r="B7" s="92"/>
+      <c r="C7" s="90"/>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1388,120 +1401,120 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="103" t="s">
+      <c r="I7" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="80"/>
-      <c r="K7" s="104"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="94"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
     </row>
-    <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="112" t="s">
+    <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="98"/>
-      <c r="C8" s="85"/>
-      <c r="D8" s="90" t="s">
+      <c r="B8" s="85"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="91"/>
-      <c r="F8" s="91"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="91"/>
-      <c r="I8" s="122" t="s">
+      <c r="E8" s="80"/>
+      <c r="F8" s="80"/>
+      <c r="G8" s="80"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="91"/>
-      <c r="K8" s="95"/>
+      <c r="J8" s="80"/>
+      <c r="K8" s="81"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
-    <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="113"/>
-      <c r="B9" s="98"/>
-      <c r="C9" s="85"/>
-      <c r="D9" s="120" t="s">
+    <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" s="115"/>
+      <c r="B9" s="85"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="80"/>
-      <c r="F9" s="80"/>
-      <c r="G9" s="80"/>
-      <c r="H9" s="81"/>
-      <c r="I9" s="103" t="s">
+      <c r="E9" s="92"/>
+      <c r="F9" s="92"/>
+      <c r="G9" s="92"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="80"/>
-      <c r="K9" s="104"/>
+      <c r="J9" s="92"/>
+      <c r="K9" s="94"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
-    <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="114"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="93"/>
-      <c r="D10" s="90" t="s">
+    <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="87"/>
+      <c r="B10" s="80"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91"/>
-      <c r="H10" s="91"/>
-      <c r="I10" s="94" t="s">
+      <c r="E10" s="80"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="80"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="91"/>
-      <c r="K10" s="95"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="81"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="20"/>
     </row>
-    <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="79" t="s">
+    <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" s="96" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="80"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="120" t="s">
+      <c r="B11" s="92"/>
+      <c r="C11" s="90"/>
+      <c r="D11" s="91" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="80"/>
-      <c r="G11" s="80"/>
-      <c r="H11" s="81"/>
-      <c r="I11" s="103" t="s">
+      <c r="E11" s="92"/>
+      <c r="F11" s="92"/>
+      <c r="G11" s="92"/>
+      <c r="H11" s="90"/>
+      <c r="I11" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="80"/>
-      <c r="K11" s="104"/>
+      <c r="J11" s="92"/>
+      <c r="K11" s="94"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
     </row>
-    <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="115" t="s">
+    <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="116" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="98"/>
-      <c r="C12" s="85"/>
-      <c r="D12" s="90" t="s">
+      <c r="B12" s="85"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="91"/>
-      <c r="I12" s="94" t="s">
+      <c r="E12" s="80"/>
+      <c r="F12" s="80"/>
+      <c r="G12" s="80"/>
+      <c r="H12" s="80"/>
+      <c r="I12" s="121" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="91"/>
-      <c r="K12" s="95"/>
+      <c r="J12" s="80"/>
+      <c r="K12" s="81"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
     </row>
-    <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="113"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="85"/>
+    <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="115"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="86"/>
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
@@ -1516,47 +1529,47 @@
       <c r="M13" s="19"/>
       <c r="O13" s="22"/>
     </row>
-    <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="114"/>
-      <c r="B14" s="91"/>
-      <c r="C14" s="93"/>
-      <c r="D14" s="116" t="s">
+    <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="87"/>
+      <c r="B14" s="80"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="122" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="80"/>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="104"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
+      <c r="G14" s="92"/>
+      <c r="H14" s="92"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="94"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
-    <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="100" t="s">
+    <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="85"/>
+      <c r="B15" s="86"/>
       <c r="C15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="111"/>
-      <c r="E15" s="91"/>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="91"/>
-      <c r="K15" s="95"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="81"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
     </row>
-    <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="84" t="s">
+    <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="85"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="25" t="s">
         <v>30</v>
       </c>
@@ -1573,48 +1586,48 @@
       <c r="L16" s="24"/>
       <c r="M16" s="24"/>
     </row>
-    <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="79" t="s">
+    <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="80"/>
-      <c r="C17" s="81"/>
-      <c r="D17" s="121" t="s">
+      <c r="B17" s="92"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="98"/>
-      <c r="F17" s="98"/>
-      <c r="G17" s="98"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="98"/>
-      <c r="J17" s="98"/>
-      <c r="K17" s="106"/>
+      <c r="E17" s="85"/>
+      <c r="F17" s="85"/>
+      <c r="G17" s="85"/>
+      <c r="H17" s="85"/>
+      <c r="I17" s="85"/>
+      <c r="J17" s="85"/>
+      <c r="K17" s="98"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
     </row>
-    <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="92" t="s">
+    <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="82" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="91"/>
-      <c r="C18" s="93"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="91"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="91"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="91"/>
-      <c r="K18" s="95"/>
+      <c r="B18" s="80"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="81"/>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
     </row>
-    <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="96" t="s">
+    <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="100" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="80"/>
-      <c r="C19" s="80"/>
+      <c r="B19" s="92"/>
+      <c r="C19" s="92"/>
       <c r="D19" s="29" t="s">
         <v>36</v>
       </c>
@@ -1628,12 +1641,12 @@
       <c r="L19" s="24"/>
       <c r="M19" s="24"/>
     </row>
-    <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="92" t="s">
+    <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="91"/>
-      <c r="C20" s="93"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="83"/>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -1645,12 +1658,12 @@
       <c r="L20" s="24"/>
       <c r="M20" s="24"/>
     </row>
-    <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="79" t="s">
+    <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A21" s="96" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="80"/>
-      <c r="C21" s="81"/>
+      <c r="B21" s="92"/>
+      <c r="C21" s="90"/>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -1662,12 +1675,12 @@
       <c r="L21" s="24"/>
       <c r="M21" s="24"/>
     </row>
-    <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="92" t="s">
+    <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A22" s="82" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="91"/>
-      <c r="C22" s="93"/>
+      <c r="B22" s="80"/>
+      <c r="C22" s="83"/>
       <c r="D22" s="33"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
@@ -1679,12 +1692,12 @@
       <c r="L22" s="34"/>
       <c r="M22" s="18"/>
     </row>
-    <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="96" t="s">
+    <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A23" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="80"/>
-      <c r="C23" s="80"/>
+      <c r="B23" s="92"/>
+      <c r="C23" s="92"/>
       <c r="D23" s="35"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1696,12 +1709,12 @@
       <c r="L23" s="36"/>
       <c r="M23" s="24"/>
     </row>
-    <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="92" t="s">
+    <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A24" s="82" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="91"/>
-      <c r="C24" s="93"/>
+      <c r="B24" s="80"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="30"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1714,12 +1727,12 @@
       <c r="M24" s="24"/>
       <c r="N24" s="24"/>
     </row>
-    <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="96" t="s">
+    <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A25" s="100" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="80"/>
-      <c r="C25" s="80"/>
+      <c r="B25" s="92"/>
+      <c r="C25" s="92"/>
       <c r="D25" s="37"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -1732,12 +1745,12 @@
       <c r="M25" s="24"/>
       <c r="N25" s="24"/>
     </row>
-    <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="92" t="s">
+    <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A26" s="82" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="91"/>
-      <c r="C26" s="93"/>
+      <c r="B26" s="80"/>
+      <c r="C26" s="83"/>
       <c r="D26" s="37"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
@@ -1750,38 +1763,38 @@
       <c r="M26" s="24"/>
       <c r="N26" s="24"/>
     </row>
-    <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="82" t="s">
+    <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A27" s="117" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="108" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="108" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="89"/>
-      <c r="E27" s="88" t="s">
+      <c r="D27" s="109"/>
+      <c r="E27" s="108" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="89"/>
+      <c r="F27" s="109"/>
       <c r="G27" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="119" t="s">
+      <c r="H27" s="89" t="s">
         <v>49</v>
       </c>
-      <c r="I27" s="81"/>
-      <c r="J27" s="110" t="s">
+      <c r="I27" s="90"/>
+      <c r="J27" s="113" t="s">
         <v>50</v>
       </c>
-      <c r="K27" s="104"/>
+      <c r="K27" s="94"/>
       <c r="L27" s="40"/>
       <c r="M27" s="40"/>
     </row>
-    <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="83"/>
-      <c r="B28" s="109"/>
+    <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A28" s="118"/>
+      <c r="B28" s="112"/>
       <c r="C28" s="38" t="s">
         <v>51</v>
       </c>
@@ -1797,16 +1810,16 @@
       <c r="G28" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="118" t="s">
+      <c r="H28" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="93"/>
-      <c r="J28" s="111"/>
-      <c r="K28" s="95"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="99"/>
+      <c r="K28" s="81"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
     </row>
-    <row r="29" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="42" t="s">
         <v>55</v>
       </c>
@@ -1823,7 +1836,7 @@
       <c r="L29" s="40"/>
       <c r="M29" s="40"/>
     </row>
-    <row r="30" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>56</v>
       </c>
@@ -1856,7 +1869,7 @@
       <c r="L30" s="40"/>
       <c r="M30" s="40"/>
     </row>
-    <row r="31" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="42" t="s">
         <v>65</v>
       </c>
@@ -1873,7 +1886,7 @@
       <c r="L31" s="40"/>
       <c r="M31" s="40"/>
     </row>
-    <row r="32" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="42"/>
       <c r="B32" s="43"/>
       <c r="C32" s="48"/>
@@ -1888,7 +1901,7 @@
       <c r="L32" s="40"/>
       <c r="M32" s="40"/>
     </row>
-    <row r="33" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="42"/>
       <c r="B33" s="16"/>
       <c r="C33" s="48"/>
@@ -1903,7 +1916,7 @@
       <c r="L33" s="40"/>
       <c r="M33" s="40"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A34" s="42"/>
       <c r="B34" s="16"/>
       <c r="C34" s="48"/>
@@ -1918,7 +1931,7 @@
       <c r="L34" s="40"/>
       <c r="M34" s="40"/>
     </row>
-    <row r="35" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="42"/>
       <c r="B35" s="16"/>
       <c r="C35" s="48"/>
@@ -1933,7 +1946,7 @@
       <c r="L35" s="40"/>
       <c r="M35" s="40"/>
     </row>
-    <row r="36" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="42"/>
       <c r="B36" s="16"/>
       <c r="C36" s="48"/>
@@ -1948,7 +1961,7 @@
       <c r="L36" s="40"/>
       <c r="M36" s="40"/>
     </row>
-    <row r="37" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="42"/>
       <c r="B37" s="16"/>
       <c r="C37" s="48"/>
@@ -1963,7 +1976,7 @@
       <c r="L37" s="40"/>
       <c r="M37" s="40"/>
     </row>
-    <row r="38" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="42"/>
       <c r="B38" s="43"/>
       <c r="C38" s="48"/>
@@ -1978,7 +1991,7 @@
       <c r="L38" s="40"/>
       <c r="M38" s="40"/>
     </row>
-    <row r="39" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="42"/>
       <c r="B39" s="43"/>
       <c r="C39" s="48"/>
@@ -1993,7 +2006,7 @@
       <c r="L39" s="40"/>
       <c r="M39" s="40"/>
     </row>
-    <row r="40" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="42"/>
       <c r="B40" s="43"/>
       <c r="C40" s="48"/>
@@ -2008,7 +2021,7 @@
       <c r="L40" s="40"/>
       <c r="M40" s="40"/>
     </row>
-    <row r="41" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="42"/>
       <c r="B41" s="16"/>
       <c r="C41" s="48"/>
@@ -2023,7 +2036,7 @@
       <c r="L41" s="40"/>
       <c r="M41" s="40"/>
     </row>
-    <row r="42" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="42"/>
       <c r="B42" s="16"/>
       <c r="C42" s="48"/>
@@ -2038,7 +2051,7 @@
       <c r="L42" s="40"/>
       <c r="M42" s="40"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" s="42"/>
       <c r="B43" s="16"/>
       <c r="C43" s="48"/>
@@ -2053,7 +2066,7 @@
       <c r="L43" s="40"/>
       <c r="M43" s="40"/>
     </row>
-    <row r="44" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="42"/>
       <c r="B44" s="16"/>
       <c r="C44" s="48"/>
@@ -2068,7 +2081,7 @@
       <c r="L44" s="40"/>
       <c r="M44" s="40"/>
     </row>
-    <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="42"/>
       <c r="B45" s="16"/>
       <c r="C45" s="48"/>
@@ -2084,7 +2097,7 @@
       <c r="O45" s="55"/>
       <c r="P45" s="54"/>
     </row>
-    <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="42"/>
       <c r="B46" s="16"/>
       <c r="C46" s="48"/>
@@ -2100,7 +2113,7 @@
       <c r="O46" s="55"/>
       <c r="P46" s="54"/>
     </row>
-    <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="42"/>
       <c r="B47" s="43"/>
       <c r="C47" s="48"/>
@@ -2116,7 +2129,7 @@
       <c r="O47" s="55"/>
       <c r="P47" s="54"/>
     </row>
-    <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="42"/>
       <c r="B48" s="16"/>
       <c r="C48" s="48"/>
@@ -2132,7 +2145,7 @@
       <c r="O48" s="55"/>
       <c r="P48" s="54"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A49" s="42"/>
       <c r="B49" s="16"/>
       <c r="C49" s="48"/>
@@ -2148,7 +2161,7 @@
       <c r="O49" s="55"/>
       <c r="P49" s="54"/>
     </row>
-    <row r="50" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="42"/>
       <c r="B50" s="16"/>
       <c r="C50" s="48"/>
@@ -2164,7 +2177,7 @@
       <c r="O50" s="55"/>
       <c r="P50" s="54"/>
     </row>
-    <row r="51" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="42"/>
       <c r="B51" s="16"/>
       <c r="C51" s="48"/>
@@ -2180,7 +2193,7 @@
       <c r="O51" s="55"/>
       <c r="P51" s="54"/>
     </row>
-    <row r="52" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="42"/>
       <c r="B52" s="16"/>
       <c r="C52" s="48"/>
@@ -2196,7 +2209,7 @@
       <c r="O52" s="55"/>
       <c r="P52" s="54"/>
     </row>
-    <row r="53" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="42"/>
       <c r="B53" s="43"/>
       <c r="C53" s="48"/>
@@ -2212,7 +2225,7 @@
       <c r="O53" s="55"/>
       <c r="P53" s="54"/>
     </row>
-    <row r="54" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="42"/>
       <c r="B54" s="16"/>
       <c r="C54" s="48"/>
@@ -2228,7 +2241,7 @@
       <c r="O54" s="55"/>
       <c r="P54" s="54"/>
     </row>
-    <row r="55" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="42"/>
       <c r="B55" s="16"/>
       <c r="C55" s="48"/>
@@ -2244,7 +2257,7 @@
       <c r="O55" s="55"/>
       <c r="P55" s="54"/>
     </row>
-    <row r="56" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="42"/>
       <c r="B56" s="16"/>
       <c r="C56" s="48"/>
@@ -2260,7 +2273,7 @@
       <c r="O56" s="55"/>
       <c r="P56" s="54"/>
     </row>
-    <row r="57" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="42"/>
       <c r="B57" s="16"/>
       <c r="C57" s="48"/>
@@ -2276,7 +2289,7 @@
       <c r="O57" s="55"/>
       <c r="P57" s="54"/>
     </row>
-    <row r="58" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="42"/>
       <c r="B58" s="43"/>
       <c r="C58" s="48"/>
@@ -2292,7 +2305,7 @@
       <c r="O58" s="55"/>
       <c r="P58" s="54"/>
     </row>
-    <row r="59" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="59"/>
       <c r="B59" s="10"/>
       <c r="C59" s="48"/>
@@ -2304,12 +2317,12 @@
       <c r="I59" s="11"/>
       <c r="J59" s="61"/>
       <c r="K59" s="53"/>
-      <c r="N59" s="99"/>
-      <c r="O59" s="98"/>
-      <c r="P59" s="98"/>
-      <c r="Q59" s="98"/>
-    </row>
-    <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N59" s="102"/>
+      <c r="O59" s="85"/>
+      <c r="P59" s="85"/>
+      <c r="Q59" s="85"/>
+    </row>
+    <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="62" t="s">
         <v>66</v>
       </c>
@@ -2324,7 +2337,7 @@
       <c r="J60" s="21"/>
       <c r="K60" s="63"/>
     </row>
-    <row r="61" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="64" t="s">
         <v>67</v>
       </c>
@@ -2339,7 +2352,7 @@
       <c r="J61" s="31"/>
       <c r="K61" s="53"/>
     </row>
-    <row r="62" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="65"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
@@ -2352,7 +2365,7 @@
       <c r="J62" s="31"/>
       <c r="K62" s="53"/>
     </row>
-    <row r="63" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="66" t="s">
         <v>68</v>
       </c>
@@ -2367,7 +2380,7 @@
       <c r="J63" s="31"/>
       <c r="K63" s="53"/>
     </row>
-    <row r="64" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="68" t="s">
         <v>69</v>
       </c>
@@ -2382,7 +2395,7 @@
       <c r="J64" s="31"/>
       <c r="K64" s="53"/>
     </row>
-    <row r="65" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="64"/>
       <c r="B65" s="31"/>
       <c r="C65" s="31"/>
@@ -2395,7 +2408,7 @@
       <c r="J65" s="31"/>
       <c r="K65" s="53"/>
     </row>
-    <row r="66" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="64"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
@@ -2409,45 +2422,45 @@
       <c r="K66" s="53"/>
       <c r="N66" s="22"/>
     </row>
-    <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="108" t="s">
+    <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A67" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="87"/>
-      <c r="C67" s="87"/>
-      <c r="D67" s="86"/>
-      <c r="E67" s="87"/>
-      <c r="F67" s="87"/>
-      <c r="G67" s="87"/>
-      <c r="H67" s="87"/>
-      <c r="I67" s="87"/>
-      <c r="J67" s="101" t="s">
+      <c r="B67" s="111"/>
+      <c r="C67" s="111"/>
+      <c r="D67" s="120"/>
+      <c r="E67" s="111"/>
+      <c r="F67" s="111"/>
+      <c r="G67" s="111"/>
+      <c r="H67" s="111"/>
+      <c r="I67" s="111"/>
+      <c r="J67" s="104" t="s">
         <v>70</v>
       </c>
-      <c r="K67" s="102"/>
+      <c r="K67" s="105"/>
       <c r="L67" s="69"/>
       <c r="M67" s="69"/>
     </row>
-    <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="97" t="s">
+    <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A68" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="98"/>
-      <c r="C68" s="98"/>
+      <c r="B68" s="85"/>
+      <c r="C68" s="85"/>
       <c r="D68" s="107"/>
-      <c r="E68" s="98"/>
-      <c r="F68" s="98"/>
-      <c r="G68" s="98"/>
-      <c r="H68" s="98"/>
-      <c r="I68" s="98"/>
-      <c r="J68" s="105" t="s">
+      <c r="E68" s="85"/>
+      <c r="F68" s="85"/>
+      <c r="G68" s="85"/>
+      <c r="H68" s="85"/>
+      <c r="I68" s="85"/>
+      <c r="J68" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="K68" s="106"/>
+      <c r="K68" s="98"/>
       <c r="L68" s="71"/>
       <c r="M68" s="71"/>
     </row>
-    <row r="69" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="70"/>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
@@ -2462,7 +2475,7 @@
       <c r="L69" s="71"/>
       <c r="M69" s="71"/>
     </row>
-    <row r="70" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="70"/>
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
@@ -2477,7 +2490,7 @@
       <c r="L70" s="71"/>
       <c r="M70" s="71"/>
     </row>
-    <row r="71" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="70"/>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
@@ -2492,7 +2505,7 @@
       <c r="L71" s="71"/>
       <c r="M71" s="71"/>
     </row>
-    <row r="72" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="70"/>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
@@ -2507,7 +2520,7 @@
       <c r="L72" s="71"/>
       <c r="M72" s="71"/>
     </row>
-    <row r="73" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="70"/>
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
@@ -2522,7 +2535,7 @@
       <c r="L73" s="71"/>
       <c r="M73" s="71"/>
     </row>
-    <row r="74" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="70"/>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
@@ -2537,7 +2550,7 @@
       <c r="L74" s="71"/>
       <c r="M74" s="71"/>
     </row>
-    <row r="75" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="73"/>
       <c r="B75" s="74"/>
       <c r="C75" s="74"/>
@@ -2550,44 +2563,10 @@
       <c r="J75" s="75"/>
       <c r="K75" s="76"/>
     </row>
-    <row r="76" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="76" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="J34:K34"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D17:K18"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="N59:Q59"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="D68:I68"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="J27:K28"/>
-    <mergeCell ref="A8:C10"/>
-    <mergeCell ref="A12:C14"/>
-    <mergeCell ref="A17:C17"/>
+  <mergeCells count="49">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A16:B16"/>
@@ -2604,6 +2583,39 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D14:K15"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="D68:I68"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="A8:C10"/>
+    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D17:K18"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D6:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15763888888888899" right="0.15763888888888899" top="0.27569444444444402" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/SOF_TEMPLATE.xlsx
+++ b/SOF_TEMPLATE.xlsx
@@ -766,7 +766,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="125">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -978,88 +978,14 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1067,20 +993,91 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1296,11 +1293,11 @@
       <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="96" t="s">
+      <c r="A2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="92"/>
-      <c r="C2" s="90"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="82"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1315,10 +1312,10 @@
       <c r="M2" s="9"/>
     </row>
     <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="84" t="s">
+      <c r="A3" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="85"/>
+      <c r="B3" s="105"/>
       <c r="C3" s="86"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
@@ -1334,9 +1331,9 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="87"/>
-      <c r="B4" s="80"/>
-      <c r="C4" s="83"/>
+      <c r="A4" s="111"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="94"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1351,49 +1348,49 @@
       <c r="M4" s="16"/>
     </row>
     <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="92"/>
-      <c r="C5" s="90"/>
-      <c r="D5" s="93" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="92"/>
-      <c r="F5" s="92"/>
-      <c r="G5" s="92"/>
-      <c r="H5" s="92"/>
-      <c r="I5" s="92"/>
-      <c r="J5" s="92"/>
-      <c r="K5" s="94"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="99"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="84" t="s">
+      <c r="A6" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="97" t="s">
+      <c r="B6" s="92"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="80"/>
-      <c r="F6" s="80"/>
-      <c r="G6" s="80"/>
-      <c r="H6" s="80"/>
-      <c r="I6" s="80"/>
-      <c r="J6" s="80"/>
-      <c r="K6" s="81"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
+      <c r="K6" s="96"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="96" t="s">
+      <c r="A7" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="92"/>
-      <c r="C7" s="90"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1401,119 +1398,119 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="93" t="s">
+      <c r="I7" s="101" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="92"/>
-      <c r="K7" s="94"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="99"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
     </row>
     <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="114" t="s">
+      <c r="A8" s="109" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="85"/>
+      <c r="B8" s="105"/>
       <c r="C8" s="86"/>
-      <c r="D8" s="95" t="s">
+      <c r="D8" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="80"/>
-      <c r="F8" s="80"/>
-      <c r="G8" s="80"/>
-      <c r="H8" s="80"/>
-      <c r="I8" s="79" t="s">
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="119" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="80"/>
-      <c r="K8" s="81"/>
+      <c r="J8" s="92"/>
+      <c r="K8" s="96"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="115"/>
-      <c r="B9" s="85"/>
+      <c r="A9" s="110"/>
+      <c r="B9" s="105"/>
       <c r="C9" s="86"/>
-      <c r="D9" s="91" t="s">
+      <c r="D9" s="113" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="92"/>
-      <c r="F9" s="92"/>
-      <c r="G9" s="92"/>
-      <c r="H9" s="90"/>
-      <c r="I9" s="93" t="s">
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="101" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="92"/>
-      <c r="K9" s="94"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="99"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
     <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="87"/>
-      <c r="B10" s="80"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="95" t="s">
+      <c r="A10" s="111"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="80"/>
-      <c r="F10" s="80"/>
-      <c r="G10" s="80"/>
-      <c r="H10" s="80"/>
-      <c r="I10" s="121" t="s">
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="80"/>
-      <c r="K10" s="81"/>
+      <c r="J10" s="92"/>
+      <c r="K10" s="96"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="20"/>
     </row>
     <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="96" t="s">
+      <c r="A11" s="80" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="92"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="91" t="s">
+      <c r="B11" s="81"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="92"/>
-      <c r="F11" s="92"/>
-      <c r="G11" s="92"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="93" t="s">
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="92"/>
-      <c r="K11" s="94"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="99"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="116" t="s">
+      <c r="A12" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="85"/>
+      <c r="B12" s="105"/>
       <c r="C12" s="86"/>
-      <c r="D12" s="95" t="s">
+      <c r="D12" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="80"/>
-      <c r="F12" s="80"/>
-      <c r="G12" s="80"/>
-      <c r="H12" s="80"/>
-      <c r="I12" s="121" t="s">
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="80"/>
-      <c r="K12" s="81"/>
+      <c r="J12" s="92"/>
+      <c r="K12" s="96"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="115"/>
-      <c r="B13" s="85"/>
+      <c r="A13" s="110"/>
+      <c r="B13" s="105"/>
       <c r="C13" s="86"/>
       <c r="D13" s="6" t="s">
         <v>25</v>
@@ -1530,43 +1527,43 @@
       <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="87"/>
-      <c r="B14" s="80"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="122" t="s">
+      <c r="A14" s="111"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="98" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="92"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="92"/>
-      <c r="H14" s="92"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="94"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="99"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
     <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="103" t="s">
+      <c r="A15" s="116" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="86"/>
       <c r="C15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="99"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="81"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="92"/>
+      <c r="F15" s="92"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92"/>
+      <c r="K15" s="96"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
     </row>
     <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="119" t="s">
+      <c r="A16" s="85" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="86"/>
@@ -1587,47 +1584,47 @@
       <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="80" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="92"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="97" t="s">
+      <c r="B17" s="81"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="123" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="85"/>
-      <c r="F17" s="85"/>
-      <c r="G17" s="85"/>
-      <c r="H17" s="85"/>
-      <c r="I17" s="85"/>
-      <c r="J17" s="85"/>
-      <c r="K17" s="98"/>
+      <c r="E17" s="105"/>
+      <c r="F17" s="105"/>
+      <c r="G17" s="105"/>
+      <c r="H17" s="105"/>
+      <c r="I17" s="105"/>
+      <c r="J17" s="105"/>
+      <c r="K17" s="103"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="82" t="s">
+      <c r="A18" s="93" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="80"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="80"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="81"/>
+      <c r="B18" s="92"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
+      <c r="K18" s="96"/>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
     </row>
     <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="100" t="s">
+      <c r="A19" s="97" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="92"/>
-      <c r="C19" s="92"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
       <c r="D19" s="29" t="s">
         <v>36</v>
       </c>
@@ -1642,11 +1639,11 @@
       <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="82" t="s">
+      <c r="A20" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="80"/>
-      <c r="C20" s="83"/>
+      <c r="B20" s="92"/>
+      <c r="C20" s="94"/>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -1659,11 +1656,11 @@
       <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="96" t="s">
+      <c r="A21" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="92"/>
-      <c r="C21" s="90"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="82"/>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -1676,11 +1673,11 @@
       <c r="M21" s="24"/>
     </row>
     <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="82" t="s">
+      <c r="A22" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="80"/>
-      <c r="C22" s="83"/>
+      <c r="B22" s="92"/>
+      <c r="C22" s="94"/>
       <c r="D22" s="33"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
@@ -1693,11 +1690,11 @@
       <c r="M22" s="18"/>
     </row>
     <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="100" t="s">
+      <c r="A23" s="97" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="92"/>
-      <c r="C23" s="92"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
       <c r="D23" s="35"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1710,11 +1707,11 @@
       <c r="M23" s="24"/>
     </row>
     <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="82" t="s">
+      <c r="A24" s="93" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="80"/>
-      <c r="C24" s="83"/>
+      <c r="B24" s="92"/>
+      <c r="C24" s="94"/>
       <c r="D24" s="30"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1728,11 +1725,11 @@
       <c r="N24" s="24"/>
     </row>
     <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="100" t="s">
+      <c r="A25" s="97" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="92"/>
-      <c r="C25" s="92"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
       <c r="D25" s="37"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -1746,11 +1743,11 @@
       <c r="N25" s="24"/>
     </row>
     <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="80"/>
-      <c r="C26" s="83"/>
+      <c r="B26" s="92"/>
+      <c r="C26" s="94"/>
       <c r="D26" s="37"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
@@ -1764,37 +1761,37 @@
       <c r="N26" s="24"/>
     </row>
     <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="117" t="s">
+      <c r="A27" s="83" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="108" t="s">
+      <c r="B27" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="108" t="s">
+      <c r="C27" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="109"/>
-      <c r="E27" s="108" t="s">
+      <c r="D27" s="90"/>
+      <c r="E27" s="89" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="109"/>
+      <c r="F27" s="90"/>
       <c r="G27" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="89" t="s">
+      <c r="H27" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="I27" s="90"/>
-      <c r="J27" s="113" t="s">
+      <c r="I27" s="82"/>
+      <c r="J27" s="108" t="s">
         <v>50</v>
       </c>
-      <c r="K27" s="94"/>
+      <c r="K27" s="99"/>
       <c r="L27" s="40"/>
       <c r="M27" s="40"/>
     </row>
     <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="118"/>
-      <c r="B28" s="112"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="107"/>
       <c r="C28" s="38" t="s">
         <v>51</v>
       </c>
@@ -1810,12 +1807,12 @@
       <c r="G28" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="88" t="s">
+      <c r="H28" s="121" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="83"/>
-      <c r="J28" s="99"/>
-      <c r="K28" s="81"/>
+      <c r="I28" s="94"/>
+      <c r="J28" s="100"/>
+      <c r="K28" s="96"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
     </row>
@@ -1926,8 +1923,8 @@
       <c r="G34" s="23"/>
       <c r="H34" s="51"/>
       <c r="I34" s="11"/>
-      <c r="J34" s="123"/>
-      <c r="K34" s="124"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="46"/>
       <c r="L34" s="40"/>
       <c r="M34" s="40"/>
     </row>
@@ -1963,7 +1960,7 @@
     </row>
     <row r="37" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="42"/>
-      <c r="B37" s="16"/>
+      <c r="B37" s="43"/>
       <c r="C37" s="48"/>
       <c r="D37" s="48"/>
       <c r="E37" s="48"/>
@@ -2008,7 +2005,7 @@
     </row>
     <row r="40" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="42"/>
-      <c r="B40" s="43"/>
+      <c r="B40" s="16"/>
       <c r="C40" s="48"/>
       <c r="D40" s="48"/>
       <c r="E40" s="48"/>
@@ -2042,12 +2039,12 @@
       <c r="C42" s="48"/>
       <c r="D42" s="48"/>
       <c r="E42" s="48"/>
-      <c r="F42" s="48"/>
+      <c r="F42" s="52"/>
       <c r="G42" s="23"/>
       <c r="H42" s="51"/>
       <c r="I42" s="11"/>
-      <c r="J42" s="45"/>
-      <c r="K42" s="46"/>
+      <c r="J42" s="78"/>
+      <c r="K42" s="77"/>
       <c r="L42" s="40"/>
       <c r="M42" s="40"/>
     </row>
@@ -2057,12 +2054,12 @@
       <c r="C43" s="48"/>
       <c r="D43" s="48"/>
       <c r="E43" s="48"/>
-      <c r="F43" s="52"/>
+      <c r="F43" s="48"/>
       <c r="G43" s="23"/>
       <c r="H43" s="51"/>
       <c r="I43" s="11"/>
-      <c r="J43" s="78"/>
-      <c r="K43" s="77"/>
+      <c r="J43" s="45"/>
+      <c r="K43" s="46"/>
       <c r="L43" s="40"/>
       <c r="M43" s="40"/>
     </row>
@@ -2075,7 +2072,7 @@
       <c r="F44" s="48"/>
       <c r="G44" s="23"/>
       <c r="H44" s="51"/>
-      <c r="I44" s="11"/>
+      <c r="I44" s="79"/>
       <c r="J44" s="45"/>
       <c r="K44" s="46"/>
       <c r="L44" s="40"/>
@@ -2317,10 +2314,10 @@
       <c r="I59" s="11"/>
       <c r="J59" s="61"/>
       <c r="K59" s="53"/>
-      <c r="N59" s="102"/>
-      <c r="O59" s="85"/>
-      <c r="P59" s="85"/>
-      <c r="Q59" s="85"/>
+      <c r="N59" s="115"/>
+      <c r="O59" s="105"/>
+      <c r="P59" s="105"/>
+      <c r="Q59" s="105"/>
     </row>
     <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="62" t="s">
@@ -2423,40 +2420,40 @@
       <c r="N66" s="22"/>
     </row>
     <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="110" t="s">
+      <c r="A67" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="111"/>
-      <c r="C67" s="111"/>
-      <c r="D67" s="120"/>
-      <c r="E67" s="111"/>
-      <c r="F67" s="111"/>
-      <c r="G67" s="111"/>
-      <c r="H67" s="111"/>
-      <c r="I67" s="111"/>
-      <c r="J67" s="104" t="s">
+      <c r="B67" s="88"/>
+      <c r="C67" s="88"/>
+      <c r="D67" s="87"/>
+      <c r="E67" s="88"/>
+      <c r="F67" s="88"/>
+      <c r="G67" s="88"/>
+      <c r="H67" s="88"/>
+      <c r="I67" s="88"/>
+      <c r="J67" s="117" t="s">
         <v>70</v>
       </c>
-      <c r="K67" s="105"/>
+      <c r="K67" s="118"/>
       <c r="L67" s="69"/>
       <c r="M67" s="69"/>
     </row>
     <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="101" t="s">
+      <c r="A68" s="114" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="85"/>
-      <c r="C68" s="85"/>
-      <c r="D68" s="107"/>
-      <c r="E68" s="85"/>
-      <c r="F68" s="85"/>
-      <c r="G68" s="85"/>
-      <c r="H68" s="85"/>
-      <c r="I68" s="85"/>
-      <c r="J68" s="106" t="s">
+      <c r="B68" s="105"/>
+      <c r="C68" s="105"/>
+      <c r="D68" s="104"/>
+      <c r="E68" s="105"/>
+      <c r="F68" s="105"/>
+      <c r="G68" s="105"/>
+      <c r="H68" s="105"/>
+      <c r="I68" s="105"/>
+      <c r="J68" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="K68" s="98"/>
+      <c r="K68" s="103"/>
       <c r="L68" s="71"/>
       <c r="M68" s="71"/>
     </row>
@@ -2567,6 +2564,39 @@
     <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D17:K18"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="D68:I68"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="A8:C10"/>
+    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A16:B16"/>
@@ -2583,39 +2613,6 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D14:K15"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="D68:I68"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="J27:K28"/>
-    <mergeCell ref="A8:C10"/>
-    <mergeCell ref="A12:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="N59:Q59"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D17:K18"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D6:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15763888888888899" right="0.15763888888888899" top="0.27569444444444402" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/SOF_TEMPLATE.xlsx
+++ b/SOF_TEMPLATE.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eun.aasmahri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27F2FFD6-100F-4F12-9AAC-AE834F531C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354E8B2F-1341-459A-8C0D-152DDD4E9866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOF (3)" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'SOF (3)'!$A$1:$K$75</definedName>
     <definedName name="Texte4" localSheetId="0">'SOF (3)'!$N$16</definedName>
     <definedName name="Texte7" localSheetId="0">'SOF (3)'!$O$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'SOF (3)'!$A$1:$K$75</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -881,9 +881,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -922,9 +919,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -978,14 +972,88 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -993,91 +1061,23 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1108,8 +1108,8 @@
       <xdr:rowOff>56520</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>70560</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>689685</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>895350</xdr:rowOff>
     </xdr:to>
@@ -1260,23 +1260,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q77"/>
-  <sheetFormatPr defaultColWidth="11.4609375" defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.84375" customWidth="1"/>
-    <col min="2" max="2" width="12.9453125" customWidth="1"/>
-    <col min="3" max="3" width="5.796875" customWidth="1"/>
-    <col min="4" max="4" width="6.60546875" customWidth="1"/>
-    <col min="5" max="6" width="5.93359375" customWidth="1"/>
-    <col min="7" max="7" width="5.52734375" customWidth="1"/>
-    <col min="8" max="8" width="12.26953125" customWidth="1"/>
-    <col min="9" max="9" width="1.6171875" customWidth="1"/>
-    <col min="10" max="10" width="24.54296875" customWidth="1"/>
-    <col min="11" max="11" width="7.55078125" customWidth="1"/>
-    <col min="12" max="12" width="0.94140625" customWidth="1"/>
-    <col min="13" max="13" width="4.58203125" customWidth="1"/>
+    <col min="1" max="1" width="13.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="5.85546875" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" customWidth="1"/>
+    <col min="5" max="6" width="6" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" customWidth="1"/>
+    <col min="9" max="9" width="1.5703125" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" customWidth="1"/>
+    <col min="11" max="11" width="26.42578125" customWidth="1"/>
+    <col min="12" max="12" width="1" customWidth="1"/>
+    <col min="13" max="13" width="4.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="75.95" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" ht="75.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1292,12 +1292,12 @@
       <c r="M1" s="4"/>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="80" t="s">
+    <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="92" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="82"/>
+      <c r="B2" s="88"/>
+      <c r="C2" s="86"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1311,12 +1311,12 @@
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
     </row>
-    <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="120" t="s">
+    <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="105"/>
-      <c r="C3" s="86"/>
+      <c r="B3" s="78"/>
+      <c r="C3" s="79"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1330,10 +1330,10 @@
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
     </row>
-    <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="111"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="94"/>
+    <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="80"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="82"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1347,50 +1347,50 @@
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
     </row>
-    <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="80" t="s">
+    <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="101" t="s">
+      <c r="B5" s="88"/>
+      <c r="C5" s="86"/>
+      <c r="D5" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="99"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="90"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
     </row>
-    <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="120" t="s">
+    <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="123" t="s">
+      <c r="B6" s="81"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
       <c r="K6" s="96"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
-    <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="80" t="s">
+    <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="82"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="86"/>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1398,120 +1398,120 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="101" t="s">
+      <c r="I7" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="81"/>
-      <c r="K7" s="99"/>
+      <c r="J7" s="88"/>
+      <c r="K7" s="90"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
     </row>
-    <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="109" t="s">
+    <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="110" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="105"/>
-      <c r="C8" s="86"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="79"/>
       <c r="D8" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="92"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="119" t="s">
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="101" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="92"/>
+      <c r="J8" s="81"/>
       <c r="K8" s="96"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
-    <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="110"/>
-      <c r="B9" s="105"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="113" t="s">
+    <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="111"/>
+      <c r="B9" s="78"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="87" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="101" t="s">
+      <c r="E9" s="88"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="J9" s="81"/>
-      <c r="K9" s="99"/>
+      <c r="J9" s="88"/>
+      <c r="K9" s="90"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
-    <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="111"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="94"/>
+    <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="80"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="82"/>
       <c r="D10" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="95" t="s">
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="119" t="s">
         <v>18</v>
       </c>
-      <c r="J10" s="92"/>
+      <c r="J10" s="81"/>
       <c r="K10" s="96"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="20"/>
     </row>
-    <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="80" t="s">
+    <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="92" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="81"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="113" t="s">
+      <c r="B11" s="88"/>
+      <c r="C11" s="86"/>
+      <c r="D11" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="101" t="s">
+      <c r="E11" s="88"/>
+      <c r="F11" s="88"/>
+      <c r="G11" s="88"/>
+      <c r="H11" s="86"/>
+      <c r="I11" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="81"/>
-      <c r="K11" s="99"/>
+      <c r="J11" s="88"/>
+      <c r="K11" s="90"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
     </row>
-    <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="105"/>
-      <c r="C12" s="86"/>
+      <c r="B12" s="78"/>
+      <c r="C12" s="79"/>
       <c r="D12" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="95" t="s">
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="92"/>
+      <c r="J12" s="81"/>
       <c r="K12" s="96"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
     </row>
-    <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="110"/>
-      <c r="B13" s="105"/>
-      <c r="C13" s="86"/>
+    <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="111"/>
+      <c r="B13" s="78"/>
+      <c r="C13" s="79"/>
       <c r="D13" s="6" t="s">
         <v>25</v>
       </c>
@@ -1526,47 +1526,47 @@
       <c r="M13" s="19"/>
       <c r="O13" s="22"/>
     </row>
-    <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="111"/>
-      <c r="B14" s="92"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="98" t="s">
+    <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="80"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="82"/>
+      <c r="D14" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="99"/>
+      <c r="E14" s="88"/>
+      <c r="F14" s="88"/>
+      <c r="G14" s="88"/>
+      <c r="H14" s="88"/>
+      <c r="I14" s="88"/>
+      <c r="J14" s="88"/>
+      <c r="K14" s="90"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
-    <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="116" t="s">
+    <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="98" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="86"/>
+      <c r="B15" s="79"/>
       <c r="C15" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="100"/>
-      <c r="E15" s="92"/>
-      <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="92"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
       <c r="K15" s="96"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
     </row>
-    <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="85" t="s">
+    <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="117" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="86"/>
+      <c r="B16" s="79"/>
       <c r="C16" s="25" t="s">
         <v>30</v>
       </c>
@@ -1583,48 +1583,48 @@
       <c r="L16" s="24"/>
       <c r="M16" s="24"/>
     </row>
-    <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="80" t="s">
+    <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="123" t="s">
+      <c r="B17" s="88"/>
+      <c r="C17" s="86"/>
+      <c r="D17" s="93" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="105"/>
-      <c r="F17" s="105"/>
-      <c r="G17" s="105"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="105"/>
-      <c r="J17" s="105"/>
-      <c r="K17" s="103"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="78"/>
+      <c r="H17" s="78"/>
+      <c r="I17" s="78"/>
+      <c r="J17" s="78"/>
+      <c r="K17" s="94"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
     </row>
-    <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="93" t="s">
+    <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="92"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="92"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="82"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
       <c r="K18" s="96"/>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
     </row>
-    <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="97" t="s">
+    <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="81"/>
+      <c r="B19" s="88"/>
+      <c r="C19" s="88"/>
       <c r="D19" s="29" t="s">
         <v>36</v>
       </c>
@@ -1638,12 +1638,12 @@
       <c r="L19" s="24"/>
       <c r="M19" s="24"/>
     </row>
-    <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="93" t="s">
+    <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="84" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="92"/>
-      <c r="C20" s="94"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="82"/>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -1655,12 +1655,12 @@
       <c r="L20" s="24"/>
       <c r="M20" s="24"/>
     </row>
-    <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="80" t="s">
+    <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="92" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="81"/>
-      <c r="C21" s="82"/>
+      <c r="B21" s="88"/>
+      <c r="C21" s="86"/>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -1672,12 +1672,12 @@
       <c r="L21" s="24"/>
       <c r="M21" s="24"/>
     </row>
-    <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="93" t="s">
+    <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="94"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="82"/>
       <c r="D22" s="33"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
@@ -1689,12 +1689,12 @@
       <c r="L22" s="34"/>
       <c r="M22" s="18"/>
     </row>
-    <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="97" t="s">
+    <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="113" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="81"/>
-      <c r="C23" s="81"/>
+      <c r="B23" s="88"/>
+      <c r="C23" s="88"/>
       <c r="D23" s="35"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1706,12 +1706,12 @@
       <c r="L23" s="36"/>
       <c r="M23" s="24"/>
     </row>
-    <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="93" t="s">
+    <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="94"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="82"/>
       <c r="D24" s="30"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1724,12 +1724,12 @@
       <c r="M24" s="24"/>
       <c r="N24" s="24"/>
     </row>
-    <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="97" t="s">
+    <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="113" t="s">
         <v>42</v>
       </c>
-      <c r="B25" s="81"/>
-      <c r="C25" s="81"/>
+      <c r="B25" s="88"/>
+      <c r="C25" s="88"/>
       <c r="D25" s="37"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -1742,12 +1742,12 @@
       <c r="M25" s="24"/>
       <c r="N25" s="24"/>
     </row>
-    <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="93" t="s">
+    <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="84" t="s">
         <v>43</v>
       </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="94"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="82"/>
       <c r="D26" s="37"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
@@ -1760,38 +1760,38 @@
       <c r="M26" s="24"/>
       <c r="N26" s="24"/>
     </row>
-    <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="83" t="s">
+    <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="115" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="89" t="s">
+      <c r="B27" s="104" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="89" t="s">
+      <c r="C27" s="104" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="90"/>
-      <c r="E27" s="89" t="s">
+      <c r="D27" s="105"/>
+      <c r="E27" s="104" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="90"/>
+      <c r="F27" s="105"/>
       <c r="G27" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="122" t="s">
+      <c r="H27" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="I27" s="82"/>
-      <c r="J27" s="108" t="s">
+      <c r="I27" s="86"/>
+      <c r="J27" s="109" t="s">
         <v>50</v>
       </c>
-      <c r="K27" s="99"/>
+      <c r="K27" s="90"/>
       <c r="L27" s="40"/>
       <c r="M27" s="40"/>
     </row>
-    <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="84"/>
-      <c r="B28" s="107"/>
+    <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="116"/>
+      <c r="B28" s="108"/>
       <c r="C28" s="38" t="s">
         <v>51</v>
       </c>
@@ -1807,520 +1807,520 @@
       <c r="G28" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="121" t="s">
+      <c r="H28" s="83" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="94"/>
-      <c r="J28" s="100"/>
+      <c r="I28" s="82"/>
+      <c r="J28" s="95"/>
       <c r="K28" s="96"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
     </row>
-    <row r="29" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="42" t="s">
+    <row r="29" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="121" t="s">
         <v>55</v>
       </c>
-      <c r="B29" s="43"/>
+      <c r="B29" s="42"/>
       <c r="C29" s="23"/>
       <c r="D29" s="23"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="43"/>
       <c r="G29" s="23"/>
       <c r="H29" s="11"/>
       <c r="I29" s="11"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="46"/>
+      <c r="J29" s="44"/>
+      <c r="K29" s="45"/>
       <c r="L29" s="40"/>
       <c r="M29" s="40"/>
     </row>
-    <row r="30" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" t="s">
+    <row r="30" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="122" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="47" t="s">
+      <c r="B30" s="46" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="49" t="s">
+      <c r="D30" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="E30" s="50" t="s">
+      <c r="E30" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="49" t="s">
         <v>61</v>
       </c>
       <c r="G30" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="H30" s="51" t="s">
+      <c r="H30" s="50" t="s">
         <v>63</v>
       </c>
       <c r="I30" s="11"/>
-      <c r="J30" s="45" t="s">
+      <c r="J30" s="44" t="s">
         <v>64</v>
       </c>
-      <c r="K30" s="46"/>
+      <c r="K30" s="45"/>
       <c r="L30" s="40"/>
       <c r="M30" s="40"/>
     </row>
-    <row r="31" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="42" t="s">
+    <row r="31" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="121" t="s">
         <v>65</v>
       </c>
-      <c r="B31" s="43"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="49"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="51"/>
+      <c r="H31" s="50"/>
       <c r="I31" s="11"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="46"/>
+      <c r="J31" s="44"/>
+      <c r="K31" s="45"/>
       <c r="L31" s="40"/>
       <c r="M31" s="40"/>
     </row>
-    <row r="32" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="42"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="48"/>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="48"/>
+    <row r="32" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="121"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
       <c r="G32" s="23"/>
-      <c r="H32" s="51"/>
+      <c r="H32" s="50"/>
       <c r="I32" s="11"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="46"/>
+      <c r="J32" s="44"/>
+      <c r="K32" s="45"/>
       <c r="L32" s="40"/>
       <c r="M32" s="40"/>
     </row>
-    <row r="33" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="42"/>
+    <row r="33" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="121"/>
       <c r="B33" s="16"/>
-      <c r="C33" s="48"/>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="48"/>
+      <c r="C33" s="47"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="47"/>
+      <c r="F33" s="47"/>
       <c r="G33" s="23"/>
-      <c r="H33" s="51"/>
+      <c r="H33" s="50"/>
       <c r="I33" s="11"/>
-      <c r="J33" s="45"/>
-      <c r="K33" s="46"/>
+      <c r="J33" s="44"/>
+      <c r="K33" s="45"/>
       <c r="L33" s="40"/>
       <c r="M33" s="40"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A34" s="42"/>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A34" s="121"/>
       <c r="B34" s="16"/>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="48"/>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="47"/>
+      <c r="F34" s="47"/>
       <c r="G34" s="23"/>
-      <c r="H34" s="51"/>
+      <c r="H34" s="50"/>
       <c r="I34" s="11"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="46"/>
+      <c r="J34" s="44"/>
+      <c r="K34" s="45"/>
       <c r="L34" s="40"/>
       <c r="M34" s="40"/>
     </row>
-    <row r="35" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="42"/>
+    <row r="35" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="121"/>
       <c r="B35" s="16"/>
-      <c r="C35" s="48"/>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="48"/>
+      <c r="C35" s="47"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="47"/>
+      <c r="F35" s="47"/>
       <c r="G35" s="23"/>
-      <c r="H35" s="51"/>
+      <c r="H35" s="50"/>
       <c r="I35" s="11"/>
-      <c r="J35" s="45"/>
-      <c r="K35" s="46"/>
+      <c r="J35" s="44"/>
+      <c r="K35" s="45"/>
       <c r="L35" s="40"/>
       <c r="M35" s="40"/>
     </row>
-    <row r="36" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="42"/>
+    <row r="36" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="121"/>
       <c r="B36" s="16"/>
-      <c r="C36" s="48"/>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="48"/>
+      <c r="C36" s="47"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="47"/>
       <c r="G36" s="23"/>
-      <c r="H36" s="51"/>
+      <c r="H36" s="50"/>
       <c r="I36" s="11"/>
-      <c r="J36" s="45"/>
-      <c r="K36" s="46"/>
+      <c r="J36" s="44"/>
+      <c r="K36" s="45"/>
       <c r="L36" s="40"/>
       <c r="M36" s="40"/>
     </row>
-    <row r="37" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="42"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
+    <row r="37" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="121"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="47"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="47"/>
+      <c r="F37" s="47"/>
       <c r="G37" s="23"/>
-      <c r="H37" s="51"/>
+      <c r="H37" s="50"/>
       <c r="I37" s="11"/>
-      <c r="J37" s="45"/>
-      <c r="K37" s="46"/>
+      <c r="J37" s="44"/>
+      <c r="K37" s="45"/>
       <c r="L37" s="40"/>
       <c r="M37" s="40"/>
     </row>
-    <row r="38" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="42"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="48"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
+    <row r="38" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="121"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="47"/>
+      <c r="D38" s="47"/>
+      <c r="E38" s="47"/>
+      <c r="F38" s="47"/>
       <c r="G38" s="23"/>
-      <c r="H38" s="51"/>
+      <c r="H38" s="50"/>
       <c r="I38" s="11"/>
-      <c r="J38" s="45"/>
-      <c r="K38" s="46"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="45"/>
       <c r="L38" s="40"/>
       <c r="M38" s="40"/>
     </row>
-    <row r="39" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="42"/>
-      <c r="B39" s="43"/>
-      <c r="C39" s="48"/>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="48"/>
+    <row r="39" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="121"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="47"/>
+      <c r="D39" s="47"/>
+      <c r="E39" s="47"/>
+      <c r="F39" s="47"/>
       <c r="G39" s="23"/>
-      <c r="H39" s="51"/>
+      <c r="H39" s="50"/>
       <c r="I39" s="11"/>
-      <c r="J39" s="45"/>
-      <c r="K39" s="46"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="45"/>
       <c r="L39" s="40"/>
       <c r="M39" s="40"/>
     </row>
-    <row r="40" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="42"/>
+    <row r="40" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="121"/>
       <c r="B40" s="16"/>
-      <c r="C40" s="48"/>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="48"/>
+      <c r="C40" s="47"/>
+      <c r="D40" s="47"/>
+      <c r="E40" s="47"/>
+      <c r="F40" s="47"/>
       <c r="G40" s="23"/>
-      <c r="H40" s="51"/>
+      <c r="H40" s="50"/>
       <c r="I40" s="11"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="46"/>
+      <c r="J40" s="44"/>
+      <c r="K40" s="45"/>
       <c r="L40" s="40"/>
       <c r="M40" s="40"/>
     </row>
-    <row r="41" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="42"/>
+    <row r="41" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="121"/>
       <c r="B41" s="16"/>
-      <c r="C41" s="48"/>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="48"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
       <c r="G41" s="23"/>
-      <c r="H41" s="51"/>
+      <c r="H41" s="50"/>
       <c r="I41" s="11"/>
-      <c r="J41" s="45"/>
-      <c r="K41" s="46"/>
+      <c r="J41" s="44"/>
+      <c r="K41" s="45"/>
       <c r="L41" s="40"/>
       <c r="M41" s="40"/>
     </row>
-    <row r="42" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="42"/>
+    <row r="42" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="121"/>
       <c r="B42" s="16"/>
-      <c r="C42" s="48"/>
-      <c r="D42" s="48"/>
-      <c r="E42" s="48"/>
-      <c r="F42" s="52"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="47"/>
+      <c r="F42" s="51"/>
       <c r="G42" s="23"/>
-      <c r="H42" s="51"/>
+      <c r="H42" s="50"/>
       <c r="I42" s="11"/>
-      <c r="J42" s="78"/>
-      <c r="K42" s="77"/>
+      <c r="J42" s="76"/>
+      <c r="K42" s="75"/>
       <c r="L42" s="40"/>
       <c r="M42" s="40"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A43" s="42"/>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A43" s="121"/>
       <c r="B43" s="16"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
+      <c r="C43" s="47"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
       <c r="G43" s="23"/>
-      <c r="H43" s="51"/>
+      <c r="H43" s="50"/>
       <c r="I43" s="11"/>
-      <c r="J43" s="45"/>
-      <c r="K43" s="46"/>
+      <c r="J43" s="44"/>
+      <c r="K43" s="45"/>
       <c r="L43" s="40"/>
       <c r="M43" s="40"/>
     </row>
-    <row r="44" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="42"/>
+    <row r="44" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="121"/>
       <c r="B44" s="16"/>
-      <c r="C44" s="48"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
       <c r="G44" s="23"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="79"/>
-      <c r="J44" s="45"/>
-      <c r="K44" s="46"/>
+      <c r="H44" s="50"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="44"/>
+      <c r="K44" s="45"/>
       <c r="L44" s="40"/>
       <c r="M44" s="40"/>
     </row>
-    <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="42"/>
+    <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="121"/>
       <c r="B45" s="16"/>
-      <c r="C45" s="48"/>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="48"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
       <c r="G45" s="23"/>
-      <c r="H45" s="51"/>
+      <c r="H45" s="50"/>
       <c r="I45" s="11"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="53"/>
-      <c r="N45" s="54"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="54"/>
-    </row>
-    <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="42"/>
+      <c r="J45" s="44"/>
+      <c r="K45" s="52"/>
+      <c r="N45" s="53"/>
+      <c r="O45" s="54"/>
+      <c r="P45" s="53"/>
+    </row>
+    <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="121"/>
       <c r="B46" s="16"/>
-      <c r="C46" s="48"/>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
       <c r="G46" s="23"/>
-      <c r="H46" s="51"/>
+      <c r="H46" s="50"/>
       <c r="I46" s="11"/>
-      <c r="J46" s="45"/>
-      <c r="K46" s="53"/>
-      <c r="N46" s="54"/>
-      <c r="O46" s="55"/>
-      <c r="P46" s="54"/>
-    </row>
-    <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="42"/>
-      <c r="B47" s="43"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
+      <c r="J46" s="44"/>
+      <c r="K46" s="52"/>
+      <c r="N46" s="53"/>
+      <c r="O46" s="54"/>
+      <c r="P46" s="53"/>
+    </row>
+    <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="121"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="47"/>
+      <c r="D47" s="47"/>
+      <c r="E47" s="47"/>
+      <c r="F47" s="47"/>
       <c r="G47" s="23"/>
-      <c r="H47" s="51"/>
+      <c r="H47" s="50"/>
       <c r="I47" s="11"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="53"/>
-      <c r="N47" s="54"/>
-      <c r="O47" s="55"/>
-      <c r="P47" s="54"/>
-    </row>
-    <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="42"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="52"/>
+      <c r="N47" s="53"/>
+      <c r="O47" s="54"/>
+      <c r="P47" s="53"/>
+    </row>
+    <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="121"/>
       <c r="B48" s="16"/>
-      <c r="C48" s="48"/>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="48"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="47"/>
+      <c r="F48" s="47"/>
       <c r="G48" s="23"/>
-      <c r="H48" s="51"/>
+      <c r="H48" s="50"/>
       <c r="I48" s="11"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="53"/>
-      <c r="N48" s="54"/>
-      <c r="O48" s="55"/>
-      <c r="P48" s="54"/>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
-      <c r="A49" s="42"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="52"/>
+      <c r="N48" s="53"/>
+      <c r="O48" s="54"/>
+      <c r="P48" s="53"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A49" s="121"/>
       <c r="B49" s="16"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
       <c r="G49" s="23"/>
-      <c r="H49" s="51"/>
+      <c r="H49" s="50"/>
       <c r="I49" s="11"/>
-      <c r="J49" s="56"/>
-      <c r="K49" s="53"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="55"/>
-      <c r="P49" s="54"/>
-    </row>
-    <row r="50" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="42"/>
+      <c r="J49" s="55"/>
+      <c r="K49" s="52"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="54"/>
+      <c r="P49" s="53"/>
+    </row>
+    <row r="50" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="121"/>
       <c r="B50" s="16"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="48"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
       <c r="G50" s="23"/>
-      <c r="H50" s="51"/>
+      <c r="H50" s="50"/>
       <c r="I50" s="11"/>
-      <c r="J50" s="45"/>
-      <c r="K50" s="53"/>
-      <c r="N50" s="54"/>
-      <c r="O50" s="55"/>
-      <c r="P50" s="54"/>
-    </row>
-    <row r="51" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="42"/>
+      <c r="J50" s="44"/>
+      <c r="K50" s="52"/>
+      <c r="N50" s="53"/>
+      <c r="O50" s="54"/>
+      <c r="P50" s="53"/>
+    </row>
+    <row r="51" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="121"/>
       <c r="B51" s="16"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="48"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="47"/>
+      <c r="F51" s="47"/>
       <c r="G51" s="23"/>
-      <c r="H51" s="51"/>
+      <c r="H51" s="50"/>
       <c r="I51" s="11"/>
-      <c r="J51" s="45"/>
-      <c r="K51" s="53"/>
-      <c r="N51" s="54"/>
-      <c r="O51" s="55"/>
-      <c r="P51" s="54"/>
-    </row>
-    <row r="52" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="42"/>
+      <c r="J51" s="44"/>
+      <c r="K51" s="52"/>
+      <c r="N51" s="53"/>
+      <c r="O51" s="54"/>
+      <c r="P51" s="53"/>
+    </row>
+    <row r="52" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="121"/>
       <c r="B52" s="16"/>
-      <c r="C52" s="48"/>
-      <c r="D52" s="48"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="48"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="47"/>
+      <c r="F52" s="47"/>
       <c r="G52" s="23"/>
-      <c r="H52" s="51"/>
+      <c r="H52" s="50"/>
       <c r="I52" s="11"/>
-      <c r="J52" s="45"/>
-      <c r="K52" s="53"/>
-      <c r="N52" s="54"/>
-      <c r="O52" s="55"/>
-      <c r="P52" s="54"/>
-    </row>
-    <row r="53" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="42"/>
-      <c r="B53" s="43"/>
-      <c r="C53" s="48"/>
-      <c r="D53" s="48"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="48"/>
+      <c r="J52" s="44"/>
+      <c r="K52" s="52"/>
+      <c r="N52" s="53"/>
+      <c r="O52" s="54"/>
+      <c r="P52" s="53"/>
+    </row>
+    <row r="53" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="121"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="47"/>
+      <c r="F53" s="47"/>
       <c r="G53" s="23"/>
-      <c r="H53" s="51"/>
+      <c r="H53" s="50"/>
       <c r="I53" s="11"/>
-      <c r="J53" s="45"/>
-      <c r="K53" s="53"/>
-      <c r="N53" s="54"/>
-      <c r="O53" s="55"/>
-      <c r="P53" s="54"/>
-    </row>
-    <row r="54" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="42"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="52"/>
+      <c r="N53" s="53"/>
+      <c r="O53" s="54"/>
+      <c r="P53" s="53"/>
+    </row>
+    <row r="54" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="121"/>
       <c r="B54" s="16"/>
-      <c r="C54" s="48"/>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="48"/>
+      <c r="C54" s="47"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="47"/>
+      <c r="F54" s="47"/>
       <c r="G54" s="23"/>
-      <c r="H54" s="51"/>
+      <c r="H54" s="50"/>
       <c r="I54" s="11"/>
-      <c r="J54" s="45"/>
-      <c r="K54" s="53"/>
-      <c r="N54" s="54"/>
-      <c r="O54" s="55"/>
-      <c r="P54" s="54"/>
-    </row>
-    <row r="55" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="42"/>
+      <c r="J54" s="44"/>
+      <c r="K54" s="52"/>
+      <c r="N54" s="53"/>
+      <c r="O54" s="54"/>
+      <c r="P54" s="53"/>
+    </row>
+    <row r="55" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="121"/>
       <c r="B55" s="16"/>
-      <c r="C55" s="48"/>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="48"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="47"/>
+      <c r="F55" s="47"/>
       <c r="G55" s="23"/>
-      <c r="H55" s="51"/>
+      <c r="H55" s="50"/>
       <c r="I55" s="11"/>
-      <c r="J55" s="45"/>
-      <c r="K55" s="53"/>
-      <c r="N55" s="54"/>
-      <c r="O55" s="55"/>
-      <c r="P55" s="54"/>
-    </row>
-    <row r="56" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="42"/>
+      <c r="J55" s="44"/>
+      <c r="K55" s="52"/>
+      <c r="N55" s="53"/>
+      <c r="O55" s="54"/>
+      <c r="P55" s="53"/>
+    </row>
+    <row r="56" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="121"/>
       <c r="B56" s="16"/>
-      <c r="C56" s="48"/>
-      <c r="D56" s="48"/>
-      <c r="E56" s="48"/>
-      <c r="F56" s="48"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="47"/>
+      <c r="F56" s="47"/>
       <c r="G56" s="23"/>
-      <c r="H56" s="51"/>
+      <c r="H56" s="50"/>
       <c r="I56" s="11"/>
-      <c r="J56" s="57"/>
-      <c r="K56" s="53"/>
-      <c r="N56" s="54"/>
-      <c r="O56" s="55"/>
-      <c r="P56" s="54"/>
-    </row>
-    <row r="57" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="42"/>
+      <c r="J56" s="56"/>
+      <c r="K56" s="52"/>
+      <c r="N56" s="53"/>
+      <c r="O56" s="54"/>
+      <c r="P56" s="53"/>
+    </row>
+    <row r="57" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="121"/>
       <c r="B57" s="16"/>
-      <c r="C57" s="48"/>
+      <c r="C57" s="47"/>
       <c r="D57" s="16"/>
-      <c r="E57" s="48"/>
-      <c r="F57" s="48"/>
+      <c r="E57" s="47"/>
+      <c r="F57" s="47"/>
       <c r="G57" s="16"/>
-      <c r="H57" s="58"/>
+      <c r="H57" s="57"/>
       <c r="I57" s="11"/>
-      <c r="J57" s="57"/>
-      <c r="K57" s="53"/>
-      <c r="N57" s="54"/>
-      <c r="O57" s="55"/>
-      <c r="P57" s="54"/>
-    </row>
-    <row r="58" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="42"/>
-      <c r="B58" s="43"/>
-      <c r="C58" s="48"/>
-      <c r="D58" s="48"/>
-      <c r="E58" s="48"/>
-      <c r="F58" s="48"/>
+      <c r="J57" s="56"/>
+      <c r="K57" s="52"/>
+      <c r="N57" s="53"/>
+      <c r="O57" s="54"/>
+      <c r="P57" s="53"/>
+    </row>
+    <row r="58" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="121"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="47"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="47"/>
+      <c r="F58" s="47"/>
       <c r="G58" s="23"/>
-      <c r="H58" s="58"/>
+      <c r="H58" s="57"/>
       <c r="I58" s="11"/>
-      <c r="J58" s="45"/>
-      <c r="K58" s="53"/>
-      <c r="N58" s="54"/>
-      <c r="O58" s="55"/>
-      <c r="P58" s="54"/>
-    </row>
-    <row r="59" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="59"/>
+      <c r="J58" s="44"/>
+      <c r="K58" s="52"/>
+      <c r="N58" s="53"/>
+      <c r="O58" s="54"/>
+      <c r="P58" s="53"/>
+    </row>
+    <row r="59" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="123"/>
       <c r="B59" s="10"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
+      <c r="C59" s="47"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
       <c r="G59" s="16"/>
-      <c r="H59" s="60"/>
+      <c r="H59" s="58"/>
       <c r="I59" s="11"/>
-      <c r="J59" s="61"/>
-      <c r="K59" s="53"/>
-      <c r="N59" s="115"/>
-      <c r="O59" s="105"/>
-      <c r="P59" s="105"/>
-      <c r="Q59" s="105"/>
-    </row>
-    <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="62" t="s">
+      <c r="J59" s="59"/>
+      <c r="K59" s="52"/>
+      <c r="N59" s="97"/>
+      <c r="O59" s="78"/>
+      <c r="P59" s="78"/>
+      <c r="Q59" s="78"/>
+    </row>
+    <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="60" t="s">
         <v>66</v>
       </c>
       <c r="B60" s="7"/>
@@ -2332,10 +2332,10 @@
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="21"/>
-      <c r="K60" s="63"/>
-    </row>
-    <row r="61" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="64" t="s">
+      <c r="K60" s="61"/>
+    </row>
+    <row r="61" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="62" t="s">
         <v>67</v>
       </c>
       <c r="B61" s="11"/>
@@ -2347,10 +2347,10 @@
       <c r="H61" s="11"/>
       <c r="I61" s="11"/>
       <c r="J61" s="31"/>
-      <c r="K61" s="53"/>
-    </row>
-    <row r="62" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="65"/>
+      <c r="K61" s="52"/>
+    </row>
+    <row r="62" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="63"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
@@ -2360,25 +2360,25 @@
       <c r="H62" s="11"/>
       <c r="I62" s="11"/>
       <c r="J62" s="31"/>
-      <c r="K62" s="53"/>
-    </row>
-    <row r="63" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="66" t="s">
+      <c r="K62" s="52"/>
+    </row>
+    <row r="63" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="64" t="s">
         <v>68</v>
       </c>
       <c r="B63" s="31"/>
-      <c r="C63" s="67"/>
-      <c r="D63" s="67"/>
-      <c r="E63" s="67"/>
+      <c r="C63" s="65"/>
+      <c r="D63" s="65"/>
+      <c r="E63" s="65"/>
       <c r="F63" s="11"/>
       <c r="G63" s="31"/>
       <c r="H63" s="11"/>
       <c r="I63" s="11"/>
       <c r="J63" s="31"/>
-      <c r="K63" s="53"/>
-    </row>
-    <row r="64" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="68" t="s">
+      <c r="K63" s="52"/>
+    </row>
+    <row r="64" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="66" t="s">
         <v>69</v>
       </c>
       <c r="B64" s="11"/>
@@ -2390,10 +2390,10 @@
       <c r="H64" s="11"/>
       <c r="I64" s="11"/>
       <c r="J64" s="31"/>
-      <c r="K64" s="53"/>
-    </row>
-    <row r="65" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="64"/>
+      <c r="K64" s="52"/>
+    </row>
+    <row r="65" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="62"/>
       <c r="B65" s="31"/>
       <c r="C65" s="31"/>
       <c r="D65" s="31"/>
@@ -2403,10 +2403,10 @@
       <c r="H65" s="11"/>
       <c r="I65" s="11"/>
       <c r="J65" s="31"/>
-      <c r="K65" s="53"/>
-    </row>
-    <row r="66" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="64"/>
+      <c r="K65" s="52"/>
+    </row>
+    <row r="66" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="62"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -2416,49 +2416,49 @@
       <c r="H66" s="11"/>
       <c r="I66" s="11"/>
       <c r="J66" s="31"/>
-      <c r="K66" s="53"/>
+      <c r="K66" s="52"/>
       <c r="N66" s="22"/>
     </row>
-    <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="88"/>
-      <c r="C67" s="88"/>
-      <c r="D67" s="87"/>
-      <c r="E67" s="88"/>
-      <c r="F67" s="88"/>
-      <c r="G67" s="88"/>
-      <c r="H67" s="88"/>
-      <c r="I67" s="88"/>
-      <c r="J67" s="117" t="s">
+      <c r="B67" s="107"/>
+      <c r="C67" s="107"/>
+      <c r="D67" s="118"/>
+      <c r="E67" s="107"/>
+      <c r="F67" s="107"/>
+      <c r="G67" s="107"/>
+      <c r="H67" s="107"/>
+      <c r="I67" s="107"/>
+      <c r="J67" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="K67" s="118"/>
-      <c r="L67" s="69"/>
-      <c r="M67" s="69"/>
-    </row>
-    <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K67" s="100"/>
+      <c r="L67" s="67"/>
+      <c r="M67" s="67"/>
+    </row>
+    <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="114" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="105"/>
-      <c r="C68" s="105"/>
-      <c r="D68" s="104"/>
-      <c r="E68" s="105"/>
-      <c r="F68" s="105"/>
-      <c r="G68" s="105"/>
-      <c r="H68" s="105"/>
-      <c r="I68" s="105"/>
+      <c r="B68" s="78"/>
+      <c r="C68" s="78"/>
+      <c r="D68" s="103"/>
+      <c r="E68" s="78"/>
+      <c r="F68" s="78"/>
+      <c r="G68" s="78"/>
+      <c r="H68" s="78"/>
+      <c r="I68" s="78"/>
       <c r="J68" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="K68" s="103"/>
-      <c r="L68" s="71"/>
-      <c r="M68" s="71"/>
-    </row>
-    <row r="69" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="70"/>
+      <c r="K68" s="94"/>
+      <c r="L68" s="69"/>
+      <c r="M68" s="69"/>
+    </row>
+    <row r="69" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="68"/>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
@@ -2467,13 +2467,13 @@
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
-      <c r="J69" s="67"/>
-      <c r="K69" s="72"/>
-      <c r="L69" s="71"/>
-      <c r="M69" s="71"/>
-    </row>
-    <row r="70" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="70"/>
+      <c r="J69" s="65"/>
+      <c r="K69" s="70"/>
+      <c r="L69" s="69"/>
+      <c r="M69" s="69"/>
+    </row>
+    <row r="70" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="68"/>
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
@@ -2482,13 +2482,13 @@
       <c r="G70" s="11"/>
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
-      <c r="J70" s="67"/>
-      <c r="K70" s="72"/>
-      <c r="L70" s="71"/>
-      <c r="M70" s="71"/>
-    </row>
-    <row r="71" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="70"/>
+      <c r="J70" s="65"/>
+      <c r="K70" s="70"/>
+      <c r="L70" s="69"/>
+      <c r="M70" s="69"/>
+    </row>
+    <row r="71" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="68"/>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
@@ -2497,13 +2497,13 @@
       <c r="G71" s="11"/>
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
-      <c r="J71" s="67"/>
-      <c r="K71" s="72"/>
-      <c r="L71" s="71"/>
-      <c r="M71" s="71"/>
-    </row>
-    <row r="72" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="70"/>
+      <c r="J71" s="65"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="69"/>
+      <c r="M71" s="69"/>
+    </row>
+    <row r="72" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="68"/>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
@@ -2512,13 +2512,13 @@
       <c r="G72" s="11"/>
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
-      <c r="J72" s="67"/>
-      <c r="K72" s="72"/>
-      <c r="L72" s="71"/>
-      <c r="M72" s="71"/>
-    </row>
-    <row r="73" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="70"/>
+      <c r="J72" s="65"/>
+      <c r="K72" s="70"/>
+      <c r="L72" s="69"/>
+      <c r="M72" s="69"/>
+    </row>
+    <row r="73" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="68"/>
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
@@ -2527,13 +2527,13 @@
       <c r="G73" s="11"/>
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
-      <c r="J73" s="67"/>
-      <c r="K73" s="72"/>
-      <c r="L73" s="71"/>
-      <c r="M73" s="71"/>
-    </row>
-    <row r="74" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="70"/>
+      <c r="J73" s="65"/>
+      <c r="K73" s="70"/>
+      <c r="L73" s="69"/>
+      <c r="M73" s="69"/>
+    </row>
+    <row r="74" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="68"/>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
@@ -2542,61 +2542,28 @@
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
-      <c r="J74" s="67"/>
-      <c r="K74" s="72"/>
-      <c r="L74" s="71"/>
-      <c r="M74" s="71"/>
-    </row>
-    <row r="75" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="73"/>
-      <c r="B75" s="74"/>
-      <c r="C75" s="74"/>
-      <c r="D75" s="74"/>
-      <c r="E75" s="74"/>
-      <c r="F75" s="74"/>
-      <c r="G75" s="74"/>
-      <c r="H75" s="74"/>
-      <c r="I75" s="74"/>
-      <c r="J75" s="75"/>
-      <c r="K75" s="76"/>
-    </row>
-    <row r="76" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.15"/>
+      <c r="J74" s="65"/>
+      <c r="K74" s="70"/>
+      <c r="L74" s="69"/>
+      <c r="M74" s="69"/>
+    </row>
+    <row r="75" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="71"/>
+      <c r="B75" s="72"/>
+      <c r="C75" s="72"/>
+      <c r="D75" s="72"/>
+      <c r="E75" s="72"/>
+      <c r="F75" s="72"/>
+      <c r="G75" s="72"/>
+      <c r="H75" s="72"/>
+      <c r="I75" s="72"/>
+      <c r="J75" s="73"/>
+      <c r="K75" s="74"/>
+    </row>
+    <row r="76" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D17:K18"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="N59:Q59"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="D68:I68"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="J27:K28"/>
-    <mergeCell ref="A8:C10"/>
-    <mergeCell ref="A12:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A16:B16"/>
@@ -2613,10 +2580,43 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D14:K15"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="D68:I68"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A8:C10"/>
+    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D17:K18"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15763888888888899" right="0.15763888888888899" top="0.27569444444444402" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="80" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/SOF_TEMPLATE.xlsx
+++ b/SOF_TEMPLATE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eun.aasmahri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354E8B2F-1341-459A-8C0D-152DDD4E9866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAA653A-585B-415C-867B-A6B003E2BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOF (3)" sheetId="1" r:id="rId1"/>
@@ -82,9 +82,6 @@
     <t>{{BERTHED_DATE}} at {{BERTHED_TIME}} hr</t>
   </si>
   <si>
-    <t>/////////////////////////////////////////////////////////////////////</t>
-  </si>
-  <si>
     <t>9. Commenced {{OPERATION_VERB}}</t>
   </si>
   <si>
@@ -257,6 +254,9 @@
   </si>
   <si>
     <t>M/V {{VESSEL_NAME}}</t>
+  </si>
+  <si>
+    <t>////////////////////////////////////////////////////////////////////</t>
   </si>
 </sst>
 </file>
@@ -972,88 +972,20 @@
     <xf numFmtId="164" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1061,23 +993,91 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1293,11 +1293,11 @@
       <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="80" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="88"/>
-      <c r="C2" s="86"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="82"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1312,11 +1312,11 @@
       <c r="M2" s="9"/>
     </row>
     <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="120" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="78"/>
-      <c r="C3" s="79"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="86"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1331,9 +1331,9 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="80"/>
-      <c r="B4" s="81"/>
-      <c r="C4" s="82"/>
+      <c r="A4" s="117"/>
+      <c r="B4" s="92"/>
+      <c r="C4" s="94"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1348,49 +1348,49 @@
       <c r="M4" s="16"/>
     </row>
     <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="88"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="89" t="s">
+      <c r="B5" s="81"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="90"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="99"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="81"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="93" t="s">
+      <c r="B6" s="92"/>
+      <c r="C6" s="94"/>
+      <c r="D6" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="81"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="81"/>
-      <c r="H6" s="81"/>
-      <c r="I6" s="81"/>
-      <c r="J6" s="81"/>
+      <c r="E6" s="92"/>
+      <c r="F6" s="92"/>
+      <c r="G6" s="92"/>
+      <c r="H6" s="92"/>
+      <c r="I6" s="92"/>
+      <c r="J6" s="92"/>
       <c r="K6" s="96"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="92" t="s">
+      <c r="A7" s="80" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="88"/>
-      <c r="C7" s="86"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="82"/>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1398,122 +1398,122 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="89" t="s">
+      <c r="I7" s="114" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="88"/>
-      <c r="K7" s="90"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="99"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
     </row>
     <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="110" t="s">
+      <c r="A8" s="115" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="78"/>
-      <c r="C8" s="79"/>
+      <c r="B8" s="104"/>
+      <c r="C8" s="86"/>
       <c r="D8" s="91" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="101" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="81"/>
+      <c r="E8" s="92"/>
+      <c r="F8" s="92"/>
+      <c r="G8" s="92"/>
+      <c r="H8" s="92"/>
+      <c r="I8" s="113" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="92"/>
       <c r="K8" s="96"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="111"/>
-      <c r="B9" s="78"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="87" t="s">
+      <c r="A9" s="116"/>
+      <c r="B9" s="104"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="119" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="82"/>
+      <c r="I9" s="114" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="88"/>
-      <c r="F9" s="88"/>
-      <c r="G9" s="88"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="89" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="88"/>
-      <c r="K9" s="90"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="99"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
     <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="80"/>
-      <c r="B10" s="81"/>
-      <c r="C10" s="82"/>
+      <c r="A10" s="117"/>
+      <c r="B10" s="92"/>
+      <c r="C10" s="94"/>
       <c r="D10" s="91" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="92"/>
+      <c r="F10" s="92"/>
+      <c r="G10" s="92"/>
+      <c r="H10" s="92"/>
+      <c r="I10" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="81"/>
-      <c r="F10" s="81"/>
-      <c r="G10" s="81"/>
-      <c r="H10" s="81"/>
-      <c r="I10" s="119" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="81"/>
+      <c r="J10" s="92"/>
       <c r="K10" s="96"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="20"/>
     </row>
     <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="92" t="s">
+      <c r="A11" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="81"/>
+      <c r="C11" s="82"/>
+      <c r="D11" s="119" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="88"/>
-      <c r="C11" s="86"/>
-      <c r="D11" s="87" t="s">
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="82"/>
+      <c r="I11" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="88"/>
-      <c r="F11" s="88"/>
-      <c r="G11" s="88"/>
-      <c r="H11" s="86"/>
-      <c r="I11" s="89" t="s">
-        <v>21</v>
-      </c>
-      <c r="J11" s="88"/>
-      <c r="K11" s="90"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="99"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="112" t="s">
+      <c r="A12" s="118" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="104"/>
+      <c r="C12" s="86"/>
+      <c r="D12" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="78"/>
-      <c r="C12" s="79"/>
-      <c r="D12" s="91" t="s">
+      <c r="E12" s="92"/>
+      <c r="F12" s="92"/>
+      <c r="G12" s="92"/>
+      <c r="H12" s="92"/>
+      <c r="I12" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="81"/>
-      <c r="F12" s="81"/>
-      <c r="G12" s="81"/>
-      <c r="H12" s="81"/>
-      <c r="I12" s="119" t="s">
-        <v>24</v>
-      </c>
-      <c r="J12" s="81"/>
+      <c r="J12" s="92"/>
       <c r="K12" s="96"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="111"/>
-      <c r="B13" s="78"/>
-      <c r="C13" s="79"/>
+      <c r="A13" s="116"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="86"/>
       <c r="D13" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
@@ -1527,51 +1527,51 @@
       <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="80"/>
-      <c r="B14" s="81"/>
-      <c r="C14" s="82"/>
-      <c r="D14" s="120" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="88"/>
-      <c r="F14" s="88"/>
-      <c r="G14" s="88"/>
-      <c r="H14" s="88"/>
-      <c r="I14" s="88"/>
-      <c r="J14" s="88"/>
-      <c r="K14" s="90"/>
+      <c r="A14" s="117"/>
+      <c r="B14" s="92"/>
+      <c r="C14" s="94"/>
+      <c r="D14" s="98" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="99"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
     <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="110" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="86"/>
+      <c r="C15" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="79"/>
-      <c r="C15" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="D15" s="95"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="81"/>
-      <c r="G15" s="81"/>
-      <c r="H15" s="81"/>
-      <c r="I15" s="81"/>
-      <c r="J15" s="81"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="92"/>
+      <c r="F15" s="92"/>
+      <c r="G15" s="92"/>
+      <c r="H15" s="92"/>
+      <c r="I15" s="92"/>
+      <c r="J15" s="92"/>
       <c r="K15" s="96"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
     </row>
     <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="117" t="s">
+      <c r="A16" s="85" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="86"/>
+      <c r="C16" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="79"/>
-      <c r="C16" s="25" t="s">
+      <c r="D16" s="6" t="s">
         <v>30</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="E16" s="26"/>
       <c r="F16" s="26"/>
@@ -1584,49 +1584,49 @@
       <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="80" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="81"/>
+      <c r="C17" s="82"/>
+      <c r="D17" s="123" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="88"/>
-      <c r="C17" s="86"/>
-      <c r="D17" s="93" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="78"/>
-      <c r="H17" s="78"/>
-      <c r="I17" s="78"/>
-      <c r="J17" s="78"/>
-      <c r="K17" s="94"/>
+      <c r="E17" s="104"/>
+      <c r="F17" s="104"/>
+      <c r="G17" s="104"/>
+      <c r="H17" s="104"/>
+      <c r="I17" s="104"/>
+      <c r="J17" s="104"/>
+      <c r="K17" s="102"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="84" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="81"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="81"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="81"/>
-      <c r="J18" s="81"/>
+      <c r="A18" s="93" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="92"/>
+      <c r="C18" s="94"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="92"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="92"/>
       <c r="K18" s="96"/>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
     </row>
     <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="113" t="s">
+      <c r="A19" s="97" t="s">
+        <v>34</v>
+      </c>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="29" t="s">
         <v>35</v>
-      </c>
-      <c r="B19" s="88"/>
-      <c r="C19" s="88"/>
-      <c r="D19" s="29" t="s">
-        <v>36</v>
       </c>
       <c r="E19" s="21"/>
       <c r="F19" s="21"/>
@@ -1639,11 +1639,11 @@
       <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="84" t="s">
-        <v>37</v>
-      </c>
-      <c r="B20" s="81"/>
-      <c r="C20" s="82"/>
+      <c r="A20" s="93" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="92"/>
+      <c r="C20" s="94"/>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -1656,11 +1656,11 @@
       <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="92" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="88"/>
-      <c r="C21" s="86"/>
+      <c r="A21" s="80" t="s">
+        <v>37</v>
+      </c>
+      <c r="B21" s="81"/>
+      <c r="C21" s="82"/>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -1673,11 +1673,11 @@
       <c r="M21" s="24"/>
     </row>
     <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="84" t="s">
-        <v>39</v>
-      </c>
-      <c r="B22" s="81"/>
-      <c r="C22" s="82"/>
+      <c r="A22" s="93" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="92"/>
+      <c r="C22" s="94"/>
       <c r="D22" s="33"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
@@ -1690,11 +1690,11 @@
       <c r="M22" s="18"/>
     </row>
     <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="113" t="s">
-        <v>40</v>
-      </c>
-      <c r="B23" s="88"/>
-      <c r="C23" s="88"/>
+      <c r="A23" s="97" t="s">
+        <v>39</v>
+      </c>
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
       <c r="D23" s="35"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1707,11 +1707,11 @@
       <c r="M23" s="24"/>
     </row>
     <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="84" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="81"/>
-      <c r="C24" s="82"/>
+      <c r="A24" s="93" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="92"/>
+      <c r="C24" s="94"/>
       <c r="D24" s="30"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1725,11 +1725,11 @@
       <c r="N24" s="24"/>
     </row>
     <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="113" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="88"/>
-      <c r="C25" s="88"/>
+      <c r="A25" s="97" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
       <c r="D25" s="37"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -1743,11 +1743,11 @@
       <c r="N25" s="24"/>
     </row>
     <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="84" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="81"/>
-      <c r="C26" s="82"/>
+      <c r="A26" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="92"/>
+      <c r="C26" s="94"/>
       <c r="D26" s="37"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
@@ -1761,64 +1761,64 @@
       <c r="N26" s="24"/>
     </row>
     <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="115" t="s">
+      <c r="A27" s="83" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="104" t="s">
+      <c r="C27" s="89" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="104" t="s">
+      <c r="D27" s="90"/>
+      <c r="E27" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="105"/>
-      <c r="E27" s="104" t="s">
+      <c r="F27" s="90"/>
+      <c r="G27" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="105"/>
-      <c r="G27" s="39" t="s">
+      <c r="H27" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="85" t="s">
+      <c r="I27" s="82"/>
+      <c r="J27" s="107" t="s">
         <v>49</v>
       </c>
-      <c r="I27" s="86"/>
-      <c r="J27" s="109" t="s">
-        <v>50</v>
-      </c>
-      <c r="K27" s="90"/>
+      <c r="K27" s="99"/>
       <c r="L27" s="40"/>
       <c r="M27" s="40"/>
     </row>
     <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="116"/>
-      <c r="B28" s="108"/>
+      <c r="A28" s="84"/>
+      <c r="B28" s="106"/>
       <c r="C28" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="E28" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>51</v>
+      </c>
+      <c r="G28" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="38" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>52</v>
-      </c>
-      <c r="G28" s="41" t="s">
+      <c r="H28" s="121" t="s">
         <v>53</v>
       </c>
-      <c r="H28" s="83" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" s="82"/>
-      <c r="J28" s="95"/>
+      <c r="I28" s="94"/>
+      <c r="J28" s="100"/>
       <c r="K28" s="96"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
     </row>
     <row r="29" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="121" t="s">
-        <v>55</v>
+      <c r="A29" s="77" t="s">
+        <v>54</v>
       </c>
       <c r="B29" s="42"/>
       <c r="C29" s="23"/>
@@ -1834,41 +1834,41 @@
       <c r="M29" s="40"/>
     </row>
     <row r="30" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="122" t="s">
+      <c r="A30" s="78" t="s">
+        <v>55</v>
+      </c>
+      <c r="B30" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B30" s="46" t="s">
+      <c r="C30" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="D30" s="48" t="s">
         <v>58</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="E30" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="E30" s="49" t="s">
+      <c r="F30" s="49" t="s">
         <v>60</v>
       </c>
-      <c r="F30" s="49" t="s">
+      <c r="G30" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="H30" s="50" t="s">
         <v>62</v>
-      </c>
-      <c r="H30" s="50" t="s">
-        <v>63</v>
       </c>
       <c r="I30" s="11"/>
       <c r="J30" s="44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="K30" s="45"/>
       <c r="L30" s="40"/>
       <c r="M30" s="40"/>
     </row>
     <row r="31" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="121" t="s">
-        <v>65</v>
+      <c r="A31" s="77" t="s">
+        <v>64</v>
       </c>
       <c r="B31" s="42"/>
       <c r="C31" s="47"/>
@@ -1884,7 +1884,7 @@
       <c r="M31" s="40"/>
     </row>
     <row r="32" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="121"/>
+      <c r="A32" s="77"/>
       <c r="B32" s="42"/>
       <c r="C32" s="47"/>
       <c r="D32" s="47"/>
@@ -1899,7 +1899,7 @@
       <c r="M32" s="40"/>
     </row>
     <row r="33" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="121"/>
+      <c r="A33" s="77"/>
       <c r="B33" s="16"/>
       <c r="C33" s="47"/>
       <c r="D33" s="47"/>
@@ -1914,7 +1914,7 @@
       <c r="M33" s="40"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A34" s="121"/>
+      <c r="A34" s="77"/>
       <c r="B34" s="16"/>
       <c r="C34" s="47"/>
       <c r="D34" s="47"/>
@@ -1929,7 +1929,7 @@
       <c r="M34" s="40"/>
     </row>
     <row r="35" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="121"/>
+      <c r="A35" s="77"/>
       <c r="B35" s="16"/>
       <c r="C35" s="47"/>
       <c r="D35" s="47"/>
@@ -1944,7 +1944,7 @@
       <c r="M35" s="40"/>
     </row>
     <row r="36" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="121"/>
+      <c r="A36" s="77"/>
       <c r="B36" s="16"/>
       <c r="C36" s="47"/>
       <c r="D36" s="47"/>
@@ -1959,7 +1959,7 @@
       <c r="M36" s="40"/>
     </row>
     <row r="37" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="121"/>
+      <c r="A37" s="77"/>
       <c r="B37" s="42"/>
       <c r="C37" s="47"/>
       <c r="D37" s="47"/>
@@ -1974,7 +1974,7 @@
       <c r="M37" s="40"/>
     </row>
     <row r="38" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="121"/>
+      <c r="A38" s="77"/>
       <c r="B38" s="42"/>
       <c r="C38" s="47"/>
       <c r="D38" s="47"/>
@@ -1989,7 +1989,7 @@
       <c r="M38" s="40"/>
     </row>
     <row r="39" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="121"/>
+      <c r="A39" s="77"/>
       <c r="B39" s="42"/>
       <c r="C39" s="47"/>
       <c r="D39" s="47"/>
@@ -2004,7 +2004,7 @@
       <c r="M39" s="40"/>
     </row>
     <row r="40" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="121"/>
+      <c r="A40" s="77"/>
       <c r="B40" s="16"/>
       <c r="C40" s="47"/>
       <c r="D40" s="47"/>
@@ -2019,7 +2019,7 @@
       <c r="M40" s="40"/>
     </row>
     <row r="41" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="121"/>
+      <c r="A41" s="77"/>
       <c r="B41" s="16"/>
       <c r="C41" s="47"/>
       <c r="D41" s="47"/>
@@ -2034,7 +2034,7 @@
       <c r="M41" s="40"/>
     </row>
     <row r="42" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="121"/>
+      <c r="A42" s="77"/>
       <c r="B42" s="16"/>
       <c r="C42" s="47"/>
       <c r="D42" s="47"/>
@@ -2049,7 +2049,7 @@
       <c r="M42" s="40"/>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A43" s="121"/>
+      <c r="A43" s="77"/>
       <c r="B43" s="16"/>
       <c r="C43" s="47"/>
       <c r="D43" s="47"/>
@@ -2064,7 +2064,7 @@
       <c r="M43" s="40"/>
     </row>
     <row r="44" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="121"/>
+      <c r="A44" s="77"/>
       <c r="B44" s="16"/>
       <c r="C44" s="47"/>
       <c r="D44" s="47"/>
@@ -2079,7 +2079,7 @@
       <c r="M44" s="40"/>
     </row>
     <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="121"/>
+      <c r="A45" s="77"/>
       <c r="B45" s="16"/>
       <c r="C45" s="47"/>
       <c r="D45" s="47"/>
@@ -2095,7 +2095,7 @@
       <c r="P45" s="53"/>
     </row>
     <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="121"/>
+      <c r="A46" s="77"/>
       <c r="B46" s="16"/>
       <c r="C46" s="47"/>
       <c r="D46" s="47"/>
@@ -2111,7 +2111,7 @@
       <c r="P46" s="53"/>
     </row>
     <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="121"/>
+      <c r="A47" s="77"/>
       <c r="B47" s="42"/>
       <c r="C47" s="47"/>
       <c r="D47" s="47"/>
@@ -2127,7 +2127,7 @@
       <c r="P47" s="53"/>
     </row>
     <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="121"/>
+      <c r="A48" s="77"/>
       <c r="B48" s="16"/>
       <c r="C48" s="47"/>
       <c r="D48" s="47"/>
@@ -2143,7 +2143,7 @@
       <c r="P48" s="53"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A49" s="121"/>
+      <c r="A49" s="77"/>
       <c r="B49" s="16"/>
       <c r="C49" s="47"/>
       <c r="D49" s="47"/>
@@ -2159,7 +2159,7 @@
       <c r="P49" s="53"/>
     </row>
     <row r="50" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="121"/>
+      <c r="A50" s="77"/>
       <c r="B50" s="16"/>
       <c r="C50" s="47"/>
       <c r="D50" s="47"/>
@@ -2175,7 +2175,7 @@
       <c r="P50" s="53"/>
     </row>
     <row r="51" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="121"/>
+      <c r="A51" s="77"/>
       <c r="B51" s="16"/>
       <c r="C51" s="47"/>
       <c r="D51" s="47"/>
@@ -2191,7 +2191,7 @@
       <c r="P51" s="53"/>
     </row>
     <row r="52" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="121"/>
+      <c r="A52" s="77"/>
       <c r="B52" s="16"/>
       <c r="C52" s="47"/>
       <c r="D52" s="47"/>
@@ -2207,7 +2207,7 @@
       <c r="P52" s="53"/>
     </row>
     <row r="53" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="121"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="42"/>
       <c r="C53" s="47"/>
       <c r="D53" s="47"/>
@@ -2223,7 +2223,7 @@
       <c r="P53" s="53"/>
     </row>
     <row r="54" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="121"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="16"/>
       <c r="C54" s="47"/>
       <c r="D54" s="47"/>
@@ -2239,7 +2239,7 @@
       <c r="P54" s="53"/>
     </row>
     <row r="55" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="121"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="16"/>
       <c r="C55" s="47"/>
       <c r="D55" s="47"/>
@@ -2255,7 +2255,7 @@
       <c r="P55" s="53"/>
     </row>
     <row r="56" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="121"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="16"/>
       <c r="C56" s="47"/>
       <c r="D56" s="47"/>
@@ -2271,7 +2271,7 @@
       <c r="P56" s="53"/>
     </row>
     <row r="57" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="121"/>
+      <c r="A57" s="77"/>
       <c r="B57" s="16"/>
       <c r="C57" s="47"/>
       <c r="D57" s="16"/>
@@ -2287,7 +2287,7 @@
       <c r="P57" s="53"/>
     </row>
     <row r="58" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="121"/>
+      <c r="A58" s="77"/>
       <c r="B58" s="42"/>
       <c r="C58" s="47"/>
       <c r="D58" s="47"/>
@@ -2303,7 +2303,7 @@
       <c r="P58" s="53"/>
     </row>
     <row r="59" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="123"/>
+      <c r="A59" s="79"/>
       <c r="B59" s="10"/>
       <c r="C59" s="47"/>
       <c r="D59" s="47"/>
@@ -2314,14 +2314,14 @@
       <c r="I59" s="11"/>
       <c r="J59" s="59"/>
       <c r="K59" s="52"/>
-      <c r="N59" s="97"/>
-      <c r="O59" s="78"/>
-      <c r="P59" s="78"/>
-      <c r="Q59" s="78"/>
+      <c r="N59" s="109"/>
+      <c r="O59" s="104"/>
+      <c r="P59" s="104"/>
+      <c r="Q59" s="104"/>
     </row>
     <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="60" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" s="7"/>
       <c r="C60" s="7"/>
@@ -2336,7 +2336,7 @@
     </row>
     <row r="61" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="62" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" s="11"/>
       <c r="C61" s="11"/>
@@ -2364,7 +2364,7 @@
     </row>
     <row r="63" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="64" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B63" s="31"/>
       <c r="C63" s="65"/>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="64" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="66" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B64" s="11"/>
       <c r="C64" s="11"/>
@@ -2420,40 +2420,40 @@
       <c r="N66" s="22"/>
     </row>
     <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="106" t="s">
+      <c r="A67" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="107"/>
-      <c r="C67" s="107"/>
-      <c r="D67" s="118"/>
-      <c r="E67" s="107"/>
-      <c r="F67" s="107"/>
-      <c r="G67" s="107"/>
-      <c r="H67" s="107"/>
-      <c r="I67" s="107"/>
-      <c r="J67" s="99" t="s">
-        <v>70</v>
-      </c>
-      <c r="K67" s="100"/>
+      <c r="B67" s="88"/>
+      <c r="C67" s="88"/>
+      <c r="D67" s="87"/>
+      <c r="E67" s="88"/>
+      <c r="F67" s="88"/>
+      <c r="G67" s="88"/>
+      <c r="H67" s="88"/>
+      <c r="I67" s="88"/>
+      <c r="J67" s="111" t="s">
+        <v>69</v>
+      </c>
+      <c r="K67" s="112"/>
       <c r="L67" s="67"/>
       <c r="M67" s="67"/>
     </row>
     <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="114" t="s">
+      <c r="A68" s="108" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="104"/>
+      <c r="C68" s="104"/>
+      <c r="D68" s="103"/>
+      <c r="E68" s="104"/>
+      <c r="F68" s="104"/>
+      <c r="G68" s="104"/>
+      <c r="H68" s="104"/>
+      <c r="I68" s="104"/>
+      <c r="J68" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="B68" s="78"/>
-      <c r="C68" s="78"/>
-      <c r="D68" s="103"/>
-      <c r="E68" s="78"/>
-      <c r="F68" s="78"/>
-      <c r="G68" s="78"/>
-      <c r="H68" s="78"/>
-      <c r="I68" s="78"/>
-      <c r="J68" s="102" t="s">
-        <v>72</v>
-      </c>
-      <c r="K68" s="94"/>
+      <c r="K68" s="102"/>
       <c r="L68" s="69"/>
       <c r="M68" s="69"/>
     </row>
@@ -2564,6 +2564,39 @@
     <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="49">
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D17:K18"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A8:C10"/>
+    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="D68:I68"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="A68:C68"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A16:B16"/>
@@ -2580,39 +2613,6 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D14:K15"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="D68:I68"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="J27:K28"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="N59:Q59"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A8:C10"/>
-    <mergeCell ref="A12:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D17:K18"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15763888888888899" right="0.15763888888888899" top="0.27569444444444402" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/SOF_TEMPLATE.xlsx
+++ b/SOF_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eun.aasmahri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAA653A-585B-415C-867B-A6B003E2BB6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0742071E-EF38-4CC3-8CC9-3D23D5414ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="74">
   <si>
     <t>1.Agent :</t>
   </si>
@@ -257,6 +257,26 @@
   </si>
   <si>
     <t>////////////////////////////////////////////////////////////////////</t>
+  </si>
+  <si>
+    <r>
+      <t>{{TUG_IN}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>{{TUG_OUT}}</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -268,7 +288,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]m/d/yyyy"/>
     <numFmt numFmtId="166" formatCode="#,##0.000;[Red]#,##0.000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -340,6 +360,10 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -766,7 +790,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="123">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -919,10 +943,6 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -981,11 +1001,88 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -993,91 +1090,17 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1260,7 +1283,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q77"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
@@ -1276,7 +1299,7 @@
     <col min="13" max="13" width="4.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="75.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="75.95" customHeight="1">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1292,12 +1315,12 @@
       <c r="M1" s="4"/>
       <c r="P1" s="5"/>
     </row>
-    <row r="2" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="80" t="s">
+    <row r="2" spans="1:16" ht="12" customHeight="1">
+      <c r="A2" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="82"/>
+      <c r="B2" s="89"/>
+      <c r="C2" s="87"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1311,12 +1334,12 @@
       <c r="L2" s="9"/>
       <c r="M2" s="9"/>
     </row>
-    <row r="3" spans="1:16" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="120" t="s">
+    <row r="3" spans="1:16" ht="11.1" customHeight="1">
+      <c r="A3" s="78" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="86"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1330,10 +1353,10 @@
       <c r="L3" s="9"/>
       <c r="M3" s="9"/>
     </row>
-    <row r="4" spans="1:16" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="117"/>
-      <c r="B4" s="92"/>
-      <c r="C4" s="94"/>
+    <row r="4" spans="1:16" ht="6.6" customHeight="1">
+      <c r="A4" s="81"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="83"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1347,50 +1370,50 @@
       <c r="L4" s="16"/>
       <c r="M4" s="16"/>
     </row>
-    <row r="5" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="80" t="s">
+    <row r="5" spans="1:16" ht="11.25" customHeight="1">
+      <c r="A5" s="93" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="81"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="114" t="s">
+      <c r="B5" s="89"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="90" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="81"/>
-      <c r="F5" s="81"/>
-      <c r="G5" s="81"/>
-      <c r="H5" s="81"/>
-      <c r="I5" s="81"/>
-      <c r="J5" s="81"/>
-      <c r="K5" s="99"/>
+      <c r="E5" s="89"/>
+      <c r="F5" s="89"/>
+      <c r="G5" s="89"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="89"/>
+      <c r="K5" s="91"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
     </row>
-    <row r="6" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="120" t="s">
+    <row r="6" spans="1:16" ht="12" customHeight="1">
+      <c r="A6" s="78" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="92"/>
-      <c r="C6" s="94"/>
-      <c r="D6" s="123" t="s">
+      <c r="B6" s="82"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="92"/>
-      <c r="F6" s="92"/>
-      <c r="G6" s="92"/>
-      <c r="H6" s="92"/>
-      <c r="I6" s="92"/>
-      <c r="J6" s="92"/>
-      <c r="K6" s="96"/>
+      <c r="E6" s="82"/>
+      <c r="F6" s="82"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="82"/>
+      <c r="I6" s="82"/>
+      <c r="J6" s="82"/>
+      <c r="K6" s="97"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
-    <row r="7" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="80" t="s">
+    <row r="7" spans="1:16" ht="11.25" customHeight="1">
+      <c r="A7" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="81"/>
-      <c r="C7" s="82"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="87"/>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1398,120 +1421,120 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="114" t="s">
+      <c r="I7" s="90" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="81"/>
-      <c r="K7" s="99"/>
+      <c r="J7" s="89"/>
+      <c r="K7" s="91"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
     </row>
-    <row r="8" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="115" t="s">
+    <row r="8" spans="1:16" ht="12" customHeight="1">
+      <c r="A8" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="104"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="91" t="s">
+      <c r="B8" s="79"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="92" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="92"/>
-      <c r="F8" s="92"/>
-      <c r="G8" s="92"/>
-      <c r="H8" s="92"/>
-      <c r="I8" s="113" t="s">
+      <c r="E8" s="82"/>
+      <c r="F8" s="82"/>
+      <c r="G8" s="82"/>
+      <c r="H8" s="82"/>
+      <c r="I8" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="92"/>
-      <c r="K8" s="96"/>
+      <c r="J8" s="82"/>
+      <c r="K8" s="97"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
-    <row r="9" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="116"/>
-      <c r="B9" s="104"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="119" t="s">
+    <row r="9" spans="1:16" ht="11.25" customHeight="1">
+      <c r="A9" s="104"/>
+      <c r="B9" s="79"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="88" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="81"/>
-      <c r="F9" s="81"/>
-      <c r="G9" s="81"/>
-      <c r="H9" s="82"/>
-      <c r="I9" s="114" t="s">
+      <c r="E9" s="89"/>
+      <c r="F9" s="89"/>
+      <c r="G9" s="89"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="90" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="81"/>
-      <c r="K9" s="99"/>
+      <c r="J9" s="89"/>
+      <c r="K9" s="91"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
-    <row r="10" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="117"/>
-      <c r="B10" s="92"/>
-      <c r="C10" s="94"/>
-      <c r="D10" s="91" t="s">
+    <row r="10" spans="1:16" ht="12" customHeight="1">
+      <c r="A10" s="81"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="83"/>
+      <c r="D10" s="92" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="92"/>
-      <c r="F10" s="92"/>
-      <c r="G10" s="92"/>
-      <c r="H10" s="92"/>
-      <c r="I10" s="95" t="s">
+      <c r="E10" s="82"/>
+      <c r="F10" s="82"/>
+      <c r="G10" s="82"/>
+      <c r="H10" s="82"/>
+      <c r="I10" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="92"/>
-      <c r="K10" s="96"/>
+      <c r="J10" s="82"/>
+      <c r="K10" s="97"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="20"/>
     </row>
-    <row r="11" spans="1:16" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="80" t="s">
+    <row r="11" spans="1:16" ht="10.5" customHeight="1">
+      <c r="A11" s="93" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="81"/>
-      <c r="C11" s="82"/>
-      <c r="D11" s="119" t="s">
+      <c r="B11" s="89"/>
+      <c r="C11" s="87"/>
+      <c r="D11" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="81"/>
-      <c r="F11" s="81"/>
-      <c r="G11" s="81"/>
-      <c r="H11" s="82"/>
-      <c r="I11" s="114" t="s">
+      <c r="E11" s="89"/>
+      <c r="F11" s="89"/>
+      <c r="G11" s="89"/>
+      <c r="H11" s="87"/>
+      <c r="I11" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="81"/>
-      <c r="K11" s="99"/>
+      <c r="J11" s="89"/>
+      <c r="K11" s="91"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
     </row>
-    <row r="12" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="118" t="s">
+    <row r="12" spans="1:16" ht="12" customHeight="1">
+      <c r="A12" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="104"/>
-      <c r="C12" s="86"/>
-      <c r="D12" s="91" t="s">
+      <c r="B12" s="79"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="92"/>
-      <c r="F12" s="92"/>
-      <c r="G12" s="92"/>
-      <c r="H12" s="92"/>
-      <c r="I12" s="95" t="s">
+      <c r="E12" s="82"/>
+      <c r="F12" s="82"/>
+      <c r="G12" s="82"/>
+      <c r="H12" s="82"/>
+      <c r="I12" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="92"/>
-      <c r="K12" s="96"/>
+      <c r="J12" s="82"/>
+      <c r="K12" s="97"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
     </row>
-    <row r="13" spans="1:16" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="116"/>
-      <c r="B13" s="104"/>
-      <c r="C13" s="86"/>
+    <row r="13" spans="1:16" ht="11.25" customHeight="1">
+      <c r="A13" s="104"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="80"/>
       <c r="D13" s="6" t="s">
         <v>24</v>
       </c>
@@ -1526,47 +1549,47 @@
       <c r="M13" s="19"/>
       <c r="O13" s="22"/>
     </row>
-    <row r="14" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="117"/>
-      <c r="B14" s="92"/>
-      <c r="C14" s="94"/>
-      <c r="D14" s="98" t="s">
+    <row r="14" spans="1:16" ht="12" customHeight="1">
+      <c r="A14" s="81"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="83"/>
+      <c r="D14" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81"/>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81"/>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="99"/>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="89"/>
+      <c r="H14" s="89"/>
+      <c r="I14" s="89"/>
+      <c r="J14" s="89"/>
+      <c r="K14" s="91"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
-    <row r="15" spans="1:16" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="110" t="s">
+    <row r="15" spans="1:16" ht="12.75" customHeight="1">
+      <c r="A15" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="86"/>
+      <c r="B15" s="80"/>
       <c r="C15" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="100"/>
-      <c r="E15" s="92"/>
-      <c r="F15" s="92"/>
-      <c r="G15" s="92"/>
-      <c r="H15" s="92"/>
-      <c r="I15" s="92"/>
-      <c r="J15" s="92"/>
-      <c r="K15" s="96"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="82"/>
+      <c r="F15" s="82"/>
+      <c r="G15" s="82"/>
+      <c r="H15" s="82"/>
+      <c r="I15" s="82"/>
+      <c r="J15" s="82"/>
+      <c r="K15" s="97"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
     </row>
-    <row r="16" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="85" t="s">
+    <row r="16" spans="1:16" ht="12.95" customHeight="1">
+      <c r="A16" s="118" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="86"/>
+      <c r="B16" s="80"/>
       <c r="C16" s="25" t="s">
         <v>29</v>
       </c>
@@ -1583,48 +1606,48 @@
       <c r="L16" s="24"/>
       <c r="M16" s="24"/>
     </row>
-    <row r="17" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="80" t="s">
+    <row r="17" spans="1:14" ht="12" customHeight="1">
+      <c r="A17" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="81"/>
-      <c r="C17" s="82"/>
-      <c r="D17" s="123" t="s">
+      <c r="B17" s="89"/>
+      <c r="C17" s="87"/>
+      <c r="D17" s="94" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="104"/>
-      <c r="F17" s="104"/>
-      <c r="G17" s="104"/>
-      <c r="H17" s="104"/>
-      <c r="I17" s="104"/>
-      <c r="J17" s="104"/>
-      <c r="K17" s="102"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="79"/>
+      <c r="G17" s="79"/>
+      <c r="H17" s="79"/>
+      <c r="I17" s="79"/>
+      <c r="J17" s="79"/>
+      <c r="K17" s="95"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
     </row>
-    <row r="18" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="93" t="s">
+    <row r="18" spans="1:14" ht="12" customHeight="1">
+      <c r="A18" s="85" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="92"/>
-      <c r="C18" s="94"/>
-      <c r="D18" s="100"/>
-      <c r="E18" s="92"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="92"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="92"/>
-      <c r="K18" s="96"/>
+      <c r="B18" s="82"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="82"/>
+      <c r="F18" s="82"/>
+      <c r="G18" s="82"/>
+      <c r="H18" s="82"/>
+      <c r="I18" s="82"/>
+      <c r="J18" s="82"/>
+      <c r="K18" s="97"/>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
     </row>
-    <row r="19" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="97" t="s">
+    <row r="19" spans="1:14" ht="11.25" customHeight="1">
+      <c r="A19" s="106" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="81"/>
-      <c r="C19" s="81"/>
+      <c r="B19" s="89"/>
+      <c r="C19" s="89"/>
       <c r="D19" s="29" t="s">
         <v>35</v>
       </c>
@@ -1638,12 +1661,12 @@
       <c r="L19" s="24"/>
       <c r="M19" s="24"/>
     </row>
-    <row r="20" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="93" t="s">
+    <row r="20" spans="1:14" ht="11.25" customHeight="1">
+      <c r="A20" s="85" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="92"/>
-      <c r="C20" s="94"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="83"/>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -1655,12 +1678,12 @@
       <c r="L20" s="24"/>
       <c r="M20" s="24"/>
     </row>
-    <row r="21" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="80" t="s">
+    <row r="21" spans="1:14" ht="11.1" customHeight="1">
+      <c r="A21" s="93" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="81"/>
-      <c r="C21" s="82"/>
+      <c r="B21" s="89"/>
+      <c r="C21" s="87"/>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -1672,12 +1695,12 @@
       <c r="L21" s="24"/>
       <c r="M21" s="24"/>
     </row>
-    <row r="22" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="93" t="s">
+    <row r="22" spans="1:14" ht="11.1" customHeight="1">
+      <c r="A22" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="92"/>
-      <c r="C22" s="94"/>
+      <c r="B22" s="82"/>
+      <c r="C22" s="83"/>
       <c r="D22" s="33"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
@@ -1689,12 +1712,12 @@
       <c r="L22" s="34"/>
       <c r="M22" s="18"/>
     </row>
-    <row r="23" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="97" t="s">
+    <row r="23" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A23" s="106" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="81"/>
-      <c r="C23" s="81"/>
+      <c r="B23" s="89"/>
+      <c r="C23" s="89"/>
       <c r="D23" s="35"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1706,12 +1729,12 @@
       <c r="L23" s="36"/>
       <c r="M23" s="24"/>
     </row>
-    <row r="24" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="93" t="s">
+    <row r="24" spans="1:14" ht="11.1" customHeight="1">
+      <c r="A24" s="85" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="92"/>
-      <c r="C24" s="94"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="83"/>
       <c r="D24" s="30"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1724,12 +1747,12 @@
       <c r="M24" s="24"/>
       <c r="N24" s="24"/>
     </row>
-    <row r="25" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="97" t="s">
+    <row r="25" spans="1:14" ht="11.25" customHeight="1">
+      <c r="A25" s="106" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="81"/>
-      <c r="C25" s="81"/>
+      <c r="B25" s="89"/>
+      <c r="C25" s="89"/>
       <c r="D25" s="37"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -1742,12 +1765,12 @@
       <c r="M25" s="24"/>
       <c r="N25" s="24"/>
     </row>
-    <row r="26" spans="1:14" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="93" t="s">
+    <row r="26" spans="1:14" ht="11.1" customHeight="1">
+      <c r="A26" s="85" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="92"/>
-      <c r="C26" s="94"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="83"/>
       <c r="D26" s="37"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
@@ -1760,38 +1783,38 @@
       <c r="M26" s="24"/>
       <c r="N26" s="24"/>
     </row>
-    <row r="27" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="83" t="s">
+    <row r="27" spans="1:14" ht="12.6" customHeight="1">
+      <c r="A27" s="116" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="89" t="s">
+      <c r="B27" s="109" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="89" t="s">
+      <c r="C27" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="90"/>
-      <c r="E27" s="89" t="s">
+      <c r="D27" s="110"/>
+      <c r="E27" s="109" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="90"/>
+      <c r="F27" s="110"/>
       <c r="G27" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="H27" s="122" t="s">
+      <c r="H27" s="86" t="s">
         <v>48</v>
       </c>
-      <c r="I27" s="82"/>
-      <c r="J27" s="107" t="s">
+      <c r="I27" s="87"/>
+      <c r="J27" s="114" t="s">
         <v>49</v>
       </c>
-      <c r="K27" s="99"/>
+      <c r="K27" s="91"/>
       <c r="L27" s="40"/>
       <c r="M27" s="40"/>
     </row>
-    <row r="28" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="84"/>
-      <c r="B28" s="106"/>
+    <row r="28" spans="1:14" ht="12.6" customHeight="1">
+      <c r="A28" s="117"/>
+      <c r="B28" s="113"/>
       <c r="C28" s="38" t="s">
         <v>50</v>
       </c>
@@ -1807,17 +1830,17 @@
       <c r="G28" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="H28" s="121" t="s">
+      <c r="H28" s="84" t="s">
         <v>53</v>
       </c>
-      <c r="I28" s="94"/>
-      <c r="J28" s="100"/>
-      <c r="K28" s="96"/>
+      <c r="I28" s="83"/>
+      <c r="J28" s="96"/>
+      <c r="K28" s="97"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
     </row>
-    <row r="29" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="77" t="s">
+    <row r="29" spans="1:14" ht="12.6" customHeight="1">
+      <c r="A29" s="75" t="s">
         <v>54</v>
       </c>
       <c r="B29" s="42"/>
@@ -1833,8 +1856,8 @@
       <c r="L29" s="40"/>
       <c r="M29" s="40"/>
     </row>
-    <row r="30" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="78" t="s">
+    <row r="30" spans="1:14" ht="12.6" customHeight="1">
+      <c r="A30" s="76" t="s">
         <v>55</v>
       </c>
       <c r="B30" s="46" t="s">
@@ -1866,8 +1889,8 @@
       <c r="L30" s="40"/>
       <c r="M30" s="40"/>
     </row>
-    <row r="31" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="77" t="s">
+    <row r="31" spans="1:14" ht="12.6" customHeight="1">
+      <c r="A31" s="75" t="s">
         <v>64</v>
       </c>
       <c r="B31" s="42"/>
@@ -1883,8 +1906,8 @@
       <c r="L31" s="40"/>
       <c r="M31" s="40"/>
     </row>
-    <row r="32" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="77"/>
+    <row r="32" spans="1:14" ht="12.6" customHeight="1">
+      <c r="A32" s="75"/>
       <c r="B32" s="42"/>
       <c r="C32" s="47"/>
       <c r="D32" s="47"/>
@@ -1898,8 +1921,8 @@
       <c r="L32" s="40"/>
       <c r="M32" s="40"/>
     </row>
-    <row r="33" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="77"/>
+    <row r="33" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A33" s="75"/>
       <c r="B33" s="16"/>
       <c r="C33" s="47"/>
       <c r="D33" s="47"/>
@@ -1913,8 +1936,8 @@
       <c r="L33" s="40"/>
       <c r="M33" s="40"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A34" s="77"/>
+    <row r="34" spans="1:16">
+      <c r="A34" s="75"/>
       <c r="B34" s="16"/>
       <c r="C34" s="47"/>
       <c r="D34" s="47"/>
@@ -1928,8 +1951,8 @@
       <c r="L34" s="40"/>
       <c r="M34" s="40"/>
     </row>
-    <row r="35" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="77"/>
+    <row r="35" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A35" s="75"/>
       <c r="B35" s="16"/>
       <c r="C35" s="47"/>
       <c r="D35" s="47"/>
@@ -1943,8 +1966,8 @@
       <c r="L35" s="40"/>
       <c r="M35" s="40"/>
     </row>
-    <row r="36" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="77"/>
+    <row r="36" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A36" s="75"/>
       <c r="B36" s="16"/>
       <c r="C36" s="47"/>
       <c r="D36" s="47"/>
@@ -1958,8 +1981,8 @@
       <c r="L36" s="40"/>
       <c r="M36" s="40"/>
     </row>
-    <row r="37" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="77"/>
+    <row r="37" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A37" s="75"/>
       <c r="B37" s="42"/>
       <c r="C37" s="47"/>
       <c r="D37" s="47"/>
@@ -1973,8 +1996,8 @@
       <c r="L37" s="40"/>
       <c r="M37" s="40"/>
     </row>
-    <row r="38" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="77"/>
+    <row r="38" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A38" s="75"/>
       <c r="B38" s="42"/>
       <c r="C38" s="47"/>
       <c r="D38" s="47"/>
@@ -1988,8 +2011,8 @@
       <c r="L38" s="40"/>
       <c r="M38" s="40"/>
     </row>
-    <row r="39" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="77"/>
+    <row r="39" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A39" s="75"/>
       <c r="B39" s="42"/>
       <c r="C39" s="47"/>
       <c r="D39" s="47"/>
@@ -2003,8 +2026,8 @@
       <c r="L39" s="40"/>
       <c r="M39" s="40"/>
     </row>
-    <row r="40" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="77"/>
+    <row r="40" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A40" s="75"/>
       <c r="B40" s="16"/>
       <c r="C40" s="47"/>
       <c r="D40" s="47"/>
@@ -2018,8 +2041,8 @@
       <c r="L40" s="40"/>
       <c r="M40" s="40"/>
     </row>
-    <row r="41" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="77"/>
+    <row r="41" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A41" s="75"/>
       <c r="B41" s="16"/>
       <c r="C41" s="47"/>
       <c r="D41" s="47"/>
@@ -2033,8 +2056,8 @@
       <c r="L41" s="40"/>
       <c r="M41" s="40"/>
     </row>
-    <row r="42" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="77"/>
+    <row r="42" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A42" s="75"/>
       <c r="B42" s="16"/>
       <c r="C42" s="47"/>
       <c r="D42" s="47"/>
@@ -2043,13 +2066,13 @@
       <c r="G42" s="23"/>
       <c r="H42" s="50"/>
       <c r="I42" s="11"/>
-      <c r="J42" s="76"/>
-      <c r="K42" s="75"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="73"/>
       <c r="L42" s="40"/>
       <c r="M42" s="40"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A43" s="77"/>
+    <row r="43" spans="1:16">
+      <c r="A43" s="75"/>
       <c r="B43" s="16"/>
       <c r="C43" s="47"/>
       <c r="D43" s="47"/>
@@ -2063,8 +2086,8 @@
       <c r="L43" s="40"/>
       <c r="M43" s="40"/>
     </row>
-    <row r="44" spans="1:16" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="77"/>
+    <row r="44" spans="1:16" ht="12.6" customHeight="1">
+      <c r="A44" s="75"/>
       <c r="B44" s="16"/>
       <c r="C44" s="47"/>
       <c r="D44" s="47"/>
@@ -2078,8 +2101,8 @@
       <c r="L44" s="40"/>
       <c r="M44" s="40"/>
     </row>
-    <row r="45" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="77"/>
+    <row r="45" spans="1:16" ht="12" customHeight="1">
+      <c r="A45" s="75"/>
       <c r="B45" s="16"/>
       <c r="C45" s="47"/>
       <c r="D45" s="47"/>
@@ -2094,8 +2117,8 @@
       <c r="O45" s="54"/>
       <c r="P45" s="53"/>
     </row>
-    <row r="46" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="77"/>
+    <row r="46" spans="1:16" ht="12" customHeight="1">
+      <c r="A46" s="75"/>
       <c r="B46" s="16"/>
       <c r="C46" s="47"/>
       <c r="D46" s="47"/>
@@ -2110,8 +2133,8 @@
       <c r="O46" s="54"/>
       <c r="P46" s="53"/>
     </row>
-    <row r="47" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="77"/>
+    <row r="47" spans="1:16" ht="12" customHeight="1">
+      <c r="A47" s="75"/>
       <c r="B47" s="42"/>
       <c r="C47" s="47"/>
       <c r="D47" s="47"/>
@@ -2126,8 +2149,8 @@
       <c r="O47" s="54"/>
       <c r="P47" s="53"/>
     </row>
-    <row r="48" spans="1:16" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="77"/>
+    <row r="48" spans="1:16" ht="12" customHeight="1">
+      <c r="A48" s="75"/>
       <c r="B48" s="16"/>
       <c r="C48" s="47"/>
       <c r="D48" s="47"/>
@@ -2142,8 +2165,8 @@
       <c r="O48" s="54"/>
       <c r="P48" s="53"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A49" s="77"/>
+    <row r="49" spans="1:17">
+      <c r="A49" s="75"/>
       <c r="B49" s="16"/>
       <c r="C49" s="47"/>
       <c r="D49" s="47"/>
@@ -2158,8 +2181,8 @@
       <c r="O49" s="54"/>
       <c r="P49" s="53"/>
     </row>
-    <row r="50" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="77"/>
+    <row r="50" spans="1:17" ht="12" customHeight="1">
+      <c r="A50" s="75"/>
       <c r="B50" s="16"/>
       <c r="C50" s="47"/>
       <c r="D50" s="47"/>
@@ -2174,8 +2197,8 @@
       <c r="O50" s="54"/>
       <c r="P50" s="53"/>
     </row>
-    <row r="51" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="77"/>
+    <row r="51" spans="1:17" ht="12" customHeight="1">
+      <c r="A51" s="75"/>
       <c r="B51" s="16"/>
       <c r="C51" s="47"/>
       <c r="D51" s="47"/>
@@ -2190,8 +2213,8 @@
       <c r="O51" s="54"/>
       <c r="P51" s="53"/>
     </row>
-    <row r="52" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="77"/>
+    <row r="52" spans="1:17" ht="12" customHeight="1">
+      <c r="A52" s="75"/>
       <c r="B52" s="16"/>
       <c r="C52" s="47"/>
       <c r="D52" s="47"/>
@@ -2206,8 +2229,8 @@
       <c r="O52" s="54"/>
       <c r="P52" s="53"/>
     </row>
-    <row r="53" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="77"/>
+    <row r="53" spans="1:17" ht="12" customHeight="1">
+      <c r="A53" s="75"/>
       <c r="B53" s="42"/>
       <c r="C53" s="47"/>
       <c r="D53" s="47"/>
@@ -2222,8 +2245,8 @@
       <c r="O53" s="54"/>
       <c r="P53" s="53"/>
     </row>
-    <row r="54" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="77"/>
+    <row r="54" spans="1:17" ht="12" customHeight="1">
+      <c r="A54" s="75"/>
       <c r="B54" s="16"/>
       <c r="C54" s="47"/>
       <c r="D54" s="47"/>
@@ -2238,8 +2261,8 @@
       <c r="O54" s="54"/>
       <c r="P54" s="53"/>
     </row>
-    <row r="55" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="77"/>
+    <row r="55" spans="1:17" ht="12" customHeight="1">
+      <c r="A55" s="75"/>
       <c r="B55" s="16"/>
       <c r="C55" s="47"/>
       <c r="D55" s="47"/>
@@ -2254,8 +2277,8 @@
       <c r="O55" s="54"/>
       <c r="P55" s="53"/>
     </row>
-    <row r="56" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="77"/>
+    <row r="56" spans="1:17" ht="12" customHeight="1">
+      <c r="A56" s="75"/>
       <c r="B56" s="16"/>
       <c r="C56" s="47"/>
       <c r="D56" s="47"/>
@@ -2270,8 +2293,8 @@
       <c r="O56" s="54"/>
       <c r="P56" s="53"/>
     </row>
-    <row r="57" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="77"/>
+    <row r="57" spans="1:17" ht="12" customHeight="1">
+      <c r="A57" s="75"/>
       <c r="B57" s="16"/>
       <c r="C57" s="47"/>
       <c r="D57" s="16"/>
@@ -2286,8 +2309,8 @@
       <c r="O57" s="54"/>
       <c r="P57" s="53"/>
     </row>
-    <row r="58" spans="1:17" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="77"/>
+    <row r="58" spans="1:17" ht="12" customHeight="1">
+      <c r="A58" s="75"/>
       <c r="B58" s="42"/>
       <c r="C58" s="47"/>
       <c r="D58" s="47"/>
@@ -2302,25 +2325,26 @@
       <c r="O58" s="54"/>
       <c r="P58" s="53"/>
     </row>
-    <row r="59" spans="1:17" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="79"/>
+    <row r="59" spans="1:17" ht="14.25" customHeight="1">
+      <c r="A59" s="77"/>
       <c r="B59" s="10"/>
-      <c r="C59" s="47"/>
-      <c r="D59" s="47"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="47"/>
-      <c r="G59" s="16"/>
-      <c r="H59" s="58"/>
-      <c r="I59" s="11"/>
-      <c r="J59" s="59"/>
+      <c r="C59" s="122" t="s">
+        <v>73</v>
+      </c>
+      <c r="D59" s="122"/>
+      <c r="E59" s="122"/>
+      <c r="F59" s="122"/>
+      <c r="G59" s="122"/>
+      <c r="H59" s="122"/>
+      <c r="I59" s="122"/>
       <c r="K59" s="52"/>
-      <c r="N59" s="109"/>
-      <c r="O59" s="104"/>
-      <c r="P59" s="104"/>
-      <c r="Q59" s="104"/>
-    </row>
-    <row r="60" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="60" t="s">
+      <c r="N59" s="98"/>
+      <c r="O59" s="79"/>
+      <c r="P59" s="79"/>
+      <c r="Q59" s="79"/>
+    </row>
+    <row r="60" spans="1:17" ht="12.75" customHeight="1">
+      <c r="A60" s="58" t="s">
         <v>65</v>
       </c>
       <c r="B60" s="7"/>
@@ -2332,10 +2356,10 @@
       <c r="H60" s="7"/>
       <c r="I60" s="7"/>
       <c r="J60" s="21"/>
-      <c r="K60" s="61"/>
-    </row>
-    <row r="61" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="62" t="s">
+      <c r="K60" s="59"/>
+    </row>
+    <row r="61" spans="1:17" ht="12.75" customHeight="1">
+      <c r="A61" s="60" t="s">
         <v>66</v>
       </c>
       <c r="B61" s="11"/>
@@ -2349,8 +2373,8 @@
       <c r="J61" s="31"/>
       <c r="K61" s="52"/>
     </row>
-    <row r="62" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="63"/>
+    <row r="62" spans="1:17" ht="12.75" customHeight="1">
+      <c r="A62" s="61"/>
       <c r="B62" s="11"/>
       <c r="C62" s="11"/>
       <c r="D62" s="11"/>
@@ -2362,14 +2386,14 @@
       <c r="J62" s="31"/>
       <c r="K62" s="52"/>
     </row>
-    <row r="63" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="64" t="s">
+    <row r="63" spans="1:17" ht="12.75" customHeight="1">
+      <c r="A63" s="62" t="s">
         <v>67</v>
       </c>
       <c r="B63" s="31"/>
-      <c r="C63" s="65"/>
-      <c r="D63" s="65"/>
-      <c r="E63" s="65"/>
+      <c r="C63" s="63"/>
+      <c r="D63" s="63"/>
+      <c r="E63" s="63"/>
       <c r="F63" s="11"/>
       <c r="G63" s="31"/>
       <c r="H63" s="11"/>
@@ -2377,8 +2401,8 @@
       <c r="J63" s="31"/>
       <c r="K63" s="52"/>
     </row>
-    <row r="64" spans="1:17" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="66" t="s">
+    <row r="64" spans="1:17" ht="12.75" customHeight="1">
+      <c r="A64" s="64" t="s">
         <v>68</v>
       </c>
       <c r="B64" s="11"/>
@@ -2392,8 +2416,8 @@
       <c r="J64" s="31"/>
       <c r="K64" s="52"/>
     </row>
-    <row r="65" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="62"/>
+    <row r="65" spans="1:14" ht="12.75" customHeight="1">
+      <c r="A65" s="60"/>
       <c r="B65" s="31"/>
       <c r="C65" s="31"/>
       <c r="D65" s="31"/>
@@ -2405,8 +2429,8 @@
       <c r="J65" s="31"/>
       <c r="K65" s="52"/>
     </row>
-    <row r="66" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="62"/>
+    <row r="66" spans="1:14" ht="12" customHeight="1">
+      <c r="A66" s="60"/>
       <c r="B66" s="11"/>
       <c r="C66" s="11"/>
       <c r="D66" s="11"/>
@@ -2419,46 +2443,46 @@
       <c r="K66" s="52"/>
       <c r="N66" s="22"/>
     </row>
-    <row r="67" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="105" t="s">
+    <row r="67" spans="1:14" ht="12.6" customHeight="1">
+      <c r="A67" s="111" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="88"/>
-      <c r="C67" s="88"/>
-      <c r="D67" s="87"/>
-      <c r="E67" s="88"/>
-      <c r="F67" s="88"/>
-      <c r="G67" s="88"/>
-      <c r="H67" s="88"/>
-      <c r="I67" s="88"/>
-      <c r="J67" s="111" t="s">
+      <c r="B67" s="112"/>
+      <c r="C67" s="112"/>
+      <c r="D67" s="119"/>
+      <c r="E67" s="112"/>
+      <c r="F67" s="112"/>
+      <c r="G67" s="112"/>
+      <c r="H67" s="112"/>
+      <c r="I67" s="112"/>
+      <c r="J67" s="100" t="s">
         <v>69</v>
       </c>
-      <c r="K67" s="112"/>
-      <c r="L67" s="67"/>
-      <c r="M67" s="67"/>
-    </row>
-    <row r="68" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="108" t="s">
+      <c r="K67" s="101"/>
+      <c r="L67" s="65"/>
+      <c r="M67" s="65"/>
+    </row>
+    <row r="68" spans="1:14" ht="12.6" customHeight="1">
+      <c r="A68" s="115" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="104"/>
-      <c r="C68" s="104"/>
-      <c r="D68" s="103"/>
-      <c r="E68" s="104"/>
-      <c r="F68" s="104"/>
-      <c r="G68" s="104"/>
-      <c r="H68" s="104"/>
-      <c r="I68" s="104"/>
-      <c r="J68" s="101" t="s">
+      <c r="B68" s="79"/>
+      <c r="C68" s="79"/>
+      <c r="D68" s="108"/>
+      <c r="E68" s="79"/>
+      <c r="F68" s="79"/>
+      <c r="G68" s="79"/>
+      <c r="H68" s="79"/>
+      <c r="I68" s="79"/>
+      <c r="J68" s="107" t="s">
         <v>71</v>
       </c>
-      <c r="K68" s="102"/>
-      <c r="L68" s="69"/>
-      <c r="M68" s="69"/>
-    </row>
-    <row r="69" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="68"/>
+      <c r="K68" s="95"/>
+      <c r="L68" s="67"/>
+      <c r="M68" s="67"/>
+    </row>
+    <row r="69" spans="1:14" ht="9.75" customHeight="1">
+      <c r="A69" s="66"/>
       <c r="B69" s="11"/>
       <c r="C69" s="11"/>
       <c r="D69" s="11"/>
@@ -2467,13 +2491,13 @@
       <c r="G69" s="11"/>
       <c r="H69" s="11"/>
       <c r="I69" s="11"/>
-      <c r="J69" s="65"/>
-      <c r="K69" s="70"/>
-      <c r="L69" s="69"/>
-      <c r="M69" s="69"/>
-    </row>
-    <row r="70" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="68"/>
+      <c r="J69" s="63"/>
+      <c r="K69" s="68"/>
+      <c r="L69" s="67"/>
+      <c r="M69" s="67"/>
+    </row>
+    <row r="70" spans="1:14" ht="9.75" customHeight="1">
+      <c r="A70" s="66"/>
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
       <c r="D70" s="11"/>
@@ -2482,13 +2506,13 @@
       <c r="G70" s="11"/>
       <c r="H70" s="11"/>
       <c r="I70" s="11"/>
-      <c r="J70" s="65"/>
-      <c r="K70" s="70"/>
-      <c r="L70" s="69"/>
-      <c r="M70" s="69"/>
-    </row>
-    <row r="71" spans="1:14" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="68"/>
+      <c r="J70" s="63"/>
+      <c r="K70" s="68"/>
+      <c r="L70" s="67"/>
+      <c r="M70" s="67"/>
+    </row>
+    <row r="71" spans="1:14" ht="9.75" customHeight="1">
+      <c r="A71" s="66"/>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
       <c r="D71" s="11"/>
@@ -2497,13 +2521,13 @@
       <c r="G71" s="11"/>
       <c r="H71" s="11"/>
       <c r="I71" s="11"/>
-      <c r="J71" s="65"/>
-      <c r="K71" s="70"/>
-      <c r="L71" s="69"/>
-      <c r="M71" s="69"/>
-    </row>
-    <row r="72" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="68"/>
+      <c r="J71" s="63"/>
+      <c r="K71" s="68"/>
+      <c r="L71" s="67"/>
+      <c r="M71" s="67"/>
+    </row>
+    <row r="72" spans="1:14" ht="12" customHeight="1">
+      <c r="A72" s="66"/>
       <c r="B72" s="11"/>
       <c r="C72" s="11"/>
       <c r="D72" s="11"/>
@@ -2512,13 +2536,13 @@
       <c r="G72" s="11"/>
       <c r="H72" s="11"/>
       <c r="I72" s="11"/>
-      <c r="J72" s="65"/>
-      <c r="K72" s="70"/>
-      <c r="L72" s="69"/>
-      <c r="M72" s="69"/>
-    </row>
-    <row r="73" spans="1:14" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="68"/>
+      <c r="J72" s="63"/>
+      <c r="K72" s="68"/>
+      <c r="L72" s="67"/>
+      <c r="M72" s="67"/>
+    </row>
+    <row r="73" spans="1:14" ht="11.25" customHeight="1">
+      <c r="A73" s="66"/>
       <c r="B73" s="11"/>
       <c r="C73" s="11"/>
       <c r="D73" s="11"/>
@@ -2527,13 +2551,13 @@
       <c r="G73" s="11"/>
       <c r="H73" s="11"/>
       <c r="I73" s="11"/>
-      <c r="J73" s="65"/>
-      <c r="K73" s="70"/>
-      <c r="L73" s="69"/>
-      <c r="M73" s="69"/>
-    </row>
-    <row r="74" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="68"/>
+      <c r="J73" s="63"/>
+      <c r="K73" s="68"/>
+      <c r="L73" s="67"/>
+      <c r="M73" s="67"/>
+    </row>
+    <row r="74" spans="1:14" ht="12" customHeight="1">
+      <c r="A74" s="66"/>
       <c r="B74" s="11"/>
       <c r="C74" s="11"/>
       <c r="D74" s="11"/>
@@ -2542,61 +2566,28 @@
       <c r="G74" s="11"/>
       <c r="H74" s="11"/>
       <c r="I74" s="11"/>
-      <c r="J74" s="65"/>
-      <c r="K74" s="70"/>
-      <c r="L74" s="69"/>
-      <c r="M74" s="69"/>
-    </row>
-    <row r="75" spans="1:14" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="71"/>
-      <c r="B75" s="72"/>
-      <c r="C75" s="72"/>
-      <c r="D75" s="72"/>
-      <c r="E75" s="72"/>
-      <c r="F75" s="72"/>
-      <c r="G75" s="72"/>
-      <c r="H75" s="72"/>
-      <c r="I75" s="72"/>
-      <c r="J75" s="73"/>
-      <c r="K75" s="74"/>
-    </row>
-    <row r="76" spans="1:14" ht="10.5" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" spans="1:14" ht="12.6" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="J74" s="63"/>
+      <c r="K74" s="68"/>
+      <c r="L74" s="67"/>
+      <c r="M74" s="67"/>
+    </row>
+    <row r="75" spans="1:14" ht="12" customHeight="1">
+      <c r="A75" s="69"/>
+      <c r="B75" s="70"/>
+      <c r="C75" s="70"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="70"/>
+      <c r="F75" s="70"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="70"/>
+      <c r="I75" s="70"/>
+      <c r="J75" s="71"/>
+      <c r="K75" s="72"/>
+    </row>
+    <row r="76" spans="1:14" ht="10.5" customHeight="1"/>
+    <row r="77" spans="1:14" ht="12.6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="49">
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D17:K18"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="N59:Q59"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A8:C10"/>
-    <mergeCell ref="A12:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="D68:I68"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="J27:K28"/>
-    <mergeCell ref="A68:C68"/>
+  <mergeCells count="50">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A16:B16"/>
@@ -2613,6 +2604,40 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D14:K15"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="D68:I68"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="C59:I59"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A8:C10"/>
+    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D17:K18"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15763888888888899" right="0.15763888888888899" top="0.27569444444444402" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>

--- a/SOF_TEMPLATE.xlsx
+++ b/SOF_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eun.aasmahri\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0742071E-EF38-4CC3-8CC9-3D23D5414ED7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBEFEE85-4522-4C8D-B69B-7AEFC0D3C46D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -260,7 +260,7 @@
   </si>
   <si>
     <r>
-      <t>{{TUG_IN}}</t>
+      <t>Tug in : {{TUG_IN}}</t>
     </r>
     <r>
       <rPr>
@@ -268,7 +268,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> / </t>
+      <t xml:space="preserve"> / Tug out : </t>
     </r>
     <r>
       <rPr>
@@ -1001,88 +1001,11 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1090,17 +1013,94 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1316,11 +1316,11 @@
       <c r="P1" s="5"/>
     </row>
     <row r="2" spans="1:16" ht="12" customHeight="1">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="78" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="89"/>
-      <c r="C2" s="87"/>
+      <c r="B2" s="79"/>
+      <c r="C2" s="80"/>
       <c r="D2" s="6" t="s">
         <v>1</v>
       </c>
@@ -1335,11 +1335,11 @@
       <c r="M2" s="9"/>
     </row>
     <row r="3" spans="1:16" ht="11.1" customHeight="1">
-      <c r="A3" s="78" t="s">
+      <c r="A3" s="119" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="79"/>
-      <c r="C3" s="80"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="84"/>
       <c r="D3" s="10" t="s">
         <v>3</v>
       </c>
@@ -1354,9 +1354,9 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:16" ht="6.6" customHeight="1">
-      <c r="A4" s="81"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="83"/>
+      <c r="A4" s="116"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="92"/>
       <c r="D4" s="13" t="s">
         <v>4</v>
       </c>
@@ -1371,49 +1371,49 @@
       <c r="M4" s="16"/>
     </row>
     <row r="5" spans="1:16" ht="11.25" customHeight="1">
-      <c r="A5" s="93" t="s">
+      <c r="A5" s="78" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="89"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="90" t="s">
+      <c r="B5" s="79"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="89"/>
-      <c r="F5" s="89"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="89"/>
-      <c r="J5" s="89"/>
-      <c r="K5" s="91"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+      <c r="J5" s="79"/>
+      <c r="K5" s="97"/>
       <c r="L5" s="17"/>
       <c r="M5" s="17"/>
     </row>
     <row r="6" spans="1:16" ht="12" customHeight="1">
-      <c r="A6" s="78" t="s">
+      <c r="A6" s="119" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="82"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="94" t="s">
+      <c r="B6" s="90"/>
+      <c r="C6" s="92"/>
+      <c r="D6" s="122" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="82"/>
-      <c r="F6" s="82"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="82"/>
-      <c r="I6" s="82"/>
-      <c r="J6" s="82"/>
-      <c r="K6" s="97"/>
+      <c r="E6" s="90"/>
+      <c r="F6" s="90"/>
+      <c r="G6" s="90"/>
+      <c r="H6" s="90"/>
+      <c r="I6" s="90"/>
+      <c r="J6" s="90"/>
+      <c r="K6" s="94"/>
       <c r="L6" s="18"/>
       <c r="M6" s="18"/>
     </row>
     <row r="7" spans="1:16" ht="11.25" customHeight="1">
-      <c r="A7" s="93" t="s">
+      <c r="A7" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="89"/>
-      <c r="C7" s="87"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="80"/>
       <c r="D7" s="6" t="s">
         <v>10</v>
       </c>
@@ -1421,120 +1421,120 @@
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="90" t="s">
+      <c r="I7" s="113" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="89"/>
-      <c r="K7" s="91"/>
+      <c r="J7" s="79"/>
+      <c r="K7" s="97"/>
       <c r="L7" s="17"/>
       <c r="M7" s="17"/>
     </row>
     <row r="8" spans="1:16" ht="12" customHeight="1">
-      <c r="A8" s="103" t="s">
+      <c r="A8" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="92" t="s">
+      <c r="B8" s="102"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="89" t="s">
         <v>13</v>
       </c>
-      <c r="E8" s="82"/>
-      <c r="F8" s="82"/>
-      <c r="G8" s="82"/>
-      <c r="H8" s="82"/>
-      <c r="I8" s="102" t="s">
+      <c r="E8" s="90"/>
+      <c r="F8" s="90"/>
+      <c r="G8" s="90"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="112" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="82"/>
-      <c r="K8" s="97"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="94"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
     </row>
     <row r="9" spans="1:16" ht="11.25" customHeight="1">
-      <c r="A9" s="104"/>
-      <c r="B9" s="79"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="88" t="s">
+      <c r="A9" s="115"/>
+      <c r="B9" s="102"/>
+      <c r="C9" s="84"/>
+      <c r="D9" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="89"/>
-      <c r="F9" s="89"/>
-      <c r="G9" s="89"/>
-      <c r="H9" s="87"/>
-      <c r="I9" s="90" t="s">
+      <c r="E9" s="79"/>
+      <c r="F9" s="79"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="113" t="s">
         <v>15</v>
       </c>
-      <c r="J9" s="89"/>
-      <c r="K9" s="91"/>
+      <c r="J9" s="79"/>
+      <c r="K9" s="97"/>
       <c r="L9" s="19"/>
       <c r="M9" s="19"/>
     </row>
     <row r="10" spans="1:16" ht="12" customHeight="1">
-      <c r="A10" s="81"/>
-      <c r="B10" s="82"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="92" t="s">
+      <c r="A10" s="116"/>
+      <c r="B10" s="90"/>
+      <c r="C10" s="92"/>
+      <c r="D10" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="82"/>
-      <c r="F10" s="82"/>
-      <c r="G10" s="82"/>
-      <c r="H10" s="82"/>
-      <c r="I10" s="120" t="s">
+      <c r="E10" s="90"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="90"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="93" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="82"/>
-      <c r="K10" s="97"/>
+      <c r="J10" s="90"/>
+      <c r="K10" s="94"/>
       <c r="L10" s="18"/>
       <c r="M10" s="18"/>
       <c r="N10" s="20"/>
     </row>
     <row r="11" spans="1:16" ht="10.5" customHeight="1">
-      <c r="A11" s="93" t="s">
+      <c r="A11" s="78" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="89"/>
-      <c r="C11" s="87"/>
-      <c r="D11" s="88" t="s">
+      <c r="B11" s="79"/>
+      <c r="C11" s="80"/>
+      <c r="D11" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="89"/>
-      <c r="H11" s="87"/>
-      <c r="I11" s="90" t="s">
+      <c r="E11" s="79"/>
+      <c r="F11" s="79"/>
+      <c r="G11" s="79"/>
+      <c r="H11" s="80"/>
+      <c r="I11" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="J11" s="89"/>
-      <c r="K11" s="91"/>
+      <c r="J11" s="79"/>
+      <c r="K11" s="97"/>
       <c r="L11" s="19"/>
       <c r="M11" s="19"/>
     </row>
     <row r="12" spans="1:16" ht="12" customHeight="1">
-      <c r="A12" s="105" t="s">
+      <c r="A12" s="117" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="79"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="92" t="s">
+      <c r="B12" s="102"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="82"/>
-      <c r="F12" s="82"/>
-      <c r="G12" s="82"/>
-      <c r="H12" s="82"/>
-      <c r="I12" s="120" t="s">
+      <c r="E12" s="90"/>
+      <c r="F12" s="90"/>
+      <c r="G12" s="90"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="93" t="s">
         <v>23</v>
       </c>
-      <c r="J12" s="82"/>
-      <c r="K12" s="97"/>
+      <c r="J12" s="90"/>
+      <c r="K12" s="94"/>
       <c r="L12" s="18"/>
       <c r="M12" s="18"/>
     </row>
     <row r="13" spans="1:16" ht="11.25" customHeight="1">
-      <c r="A13" s="104"/>
-      <c r="B13" s="79"/>
-      <c r="C13" s="80"/>
+      <c r="A13" s="115"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="84"/>
       <c r="D13" s="6" t="s">
         <v>24</v>
       </c>
@@ -1550,46 +1550,46 @@
       <c r="O13" s="22"/>
     </row>
     <row r="14" spans="1:16" ht="12" customHeight="1">
-      <c r="A14" s="81"/>
-      <c r="B14" s="82"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="121" t="s">
+      <c r="A14" s="116"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="96" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
-      <c r="G14" s="89"/>
-      <c r="H14" s="89"/>
-      <c r="I14" s="89"/>
-      <c r="J14" s="89"/>
-      <c r="K14" s="91"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="79"/>
+      <c r="G14" s="79"/>
+      <c r="H14" s="79"/>
+      <c r="I14" s="79"/>
+      <c r="J14" s="79"/>
+      <c r="K14" s="97"/>
       <c r="L14" s="18"/>
       <c r="M14" s="18"/>
     </row>
     <row r="15" spans="1:16" ht="12.75" customHeight="1">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="80"/>
+      <c r="B15" s="84"/>
       <c r="C15" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="96"/>
-      <c r="E15" s="82"/>
-      <c r="F15" s="82"/>
-      <c r="G15" s="82"/>
-      <c r="H15" s="82"/>
-      <c r="I15" s="82"/>
-      <c r="J15" s="82"/>
-      <c r="K15" s="97"/>
+      <c r="D15" s="98"/>
+      <c r="E15" s="90"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="90"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="90"/>
+      <c r="J15" s="90"/>
+      <c r="K15" s="94"/>
       <c r="L15" s="24"/>
       <c r="M15" s="24"/>
     </row>
     <row r="16" spans="1:16" ht="12.95" customHeight="1">
-      <c r="A16" s="118" t="s">
+      <c r="A16" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="80"/>
+      <c r="B16" s="84"/>
       <c r="C16" s="25" t="s">
         <v>29</v>
       </c>
@@ -1607,47 +1607,47 @@
       <c r="M16" s="24"/>
     </row>
     <row r="17" spans="1:14" ht="12" customHeight="1">
-      <c r="A17" s="93" t="s">
+      <c r="A17" s="78" t="s">
         <v>31</v>
       </c>
-      <c r="B17" s="89"/>
-      <c r="C17" s="87"/>
-      <c r="D17" s="94" t="s">
+      <c r="B17" s="79"/>
+      <c r="C17" s="80"/>
+      <c r="D17" s="122" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="79"/>
-      <c r="F17" s="79"/>
-      <c r="G17" s="79"/>
-      <c r="H17" s="79"/>
-      <c r="I17" s="79"/>
-      <c r="J17" s="79"/>
-      <c r="K17" s="95"/>
+      <c r="E17" s="102"/>
+      <c r="F17" s="102"/>
+      <c r="G17" s="102"/>
+      <c r="H17" s="102"/>
+      <c r="I17" s="102"/>
+      <c r="J17" s="102"/>
+      <c r="K17" s="100"/>
       <c r="L17" s="28"/>
       <c r="M17" s="28"/>
     </row>
     <row r="18" spans="1:14" ht="12" customHeight="1">
-      <c r="A18" s="85" t="s">
+      <c r="A18" s="91" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="82"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="97"/>
+      <c r="B18" s="90"/>
+      <c r="C18" s="92"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="90"/>
+      <c r="H18" s="90"/>
+      <c r="I18" s="90"/>
+      <c r="J18" s="90"/>
+      <c r="K18" s="94"/>
       <c r="L18" s="28"/>
       <c r="M18" s="28"/>
     </row>
     <row r="19" spans="1:14" ht="11.25" customHeight="1">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="95" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="89"/>
-      <c r="C19" s="89"/>
+      <c r="B19" s="79"/>
+      <c r="C19" s="79"/>
       <c r="D19" s="29" t="s">
         <v>35</v>
       </c>
@@ -1662,11 +1662,11 @@
       <c r="M19" s="24"/>
     </row>
     <row r="20" spans="1:14" ht="11.25" customHeight="1">
-      <c r="A20" s="85" t="s">
+      <c r="A20" s="91" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="82"/>
-      <c r="C20" s="83"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="92"/>
       <c r="D20" s="30"/>
       <c r="E20" s="31"/>
       <c r="F20" s="31"/>
@@ -1679,11 +1679,11 @@
       <c r="M20" s="24"/>
     </row>
     <row r="21" spans="1:14" ht="11.1" customHeight="1">
-      <c r="A21" s="93" t="s">
+      <c r="A21" s="78" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="89"/>
-      <c r="C21" s="87"/>
+      <c r="B21" s="79"/>
+      <c r="C21" s="80"/>
       <c r="D21" s="32"/>
       <c r="E21" s="31"/>
       <c r="F21" s="31"/>
@@ -1696,11 +1696,11 @@
       <c r="M21" s="24"/>
     </row>
     <row r="22" spans="1:14" ht="11.1" customHeight="1">
-      <c r="A22" s="85" t="s">
+      <c r="A22" s="91" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="82"/>
-      <c r="C22" s="83"/>
+      <c r="B22" s="90"/>
+      <c r="C22" s="92"/>
       <c r="D22" s="33"/>
       <c r="E22" s="31"/>
       <c r="F22" s="31"/>
@@ -1713,11 +1713,11 @@
       <c r="M22" s="18"/>
     </row>
     <row r="23" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A23" s="106" t="s">
+      <c r="A23" s="95" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="89"/>
-      <c r="C23" s="89"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="79"/>
       <c r="D23" s="35"/>
       <c r="E23" s="31"/>
       <c r="F23" s="31"/>
@@ -1730,11 +1730,11 @@
       <c r="M23" s="24"/>
     </row>
     <row r="24" spans="1:14" ht="11.1" customHeight="1">
-      <c r="A24" s="85" t="s">
+      <c r="A24" s="91" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="82"/>
-      <c r="C24" s="83"/>
+      <c r="B24" s="90"/>
+      <c r="C24" s="92"/>
       <c r="D24" s="30"/>
       <c r="E24" s="31"/>
       <c r="F24" s="31"/>
@@ -1748,11 +1748,11 @@
       <c r="N24" s="24"/>
     </row>
     <row r="25" spans="1:14" ht="11.25" customHeight="1">
-      <c r="A25" s="106" t="s">
+      <c r="A25" s="95" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="89"/>
-      <c r="C25" s="89"/>
+      <c r="B25" s="79"/>
+      <c r="C25" s="79"/>
       <c r="D25" s="37"/>
       <c r="E25" s="31"/>
       <c r="F25" s="31"/>
@@ -1766,11 +1766,11 @@
       <c r="N25" s="24"/>
     </row>
     <row r="26" spans="1:14" ht="11.1" customHeight="1">
-      <c r="A26" s="85" t="s">
+      <c r="A26" s="91" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="82"/>
-      <c r="C26" s="83"/>
+      <c r="B26" s="90"/>
+      <c r="C26" s="92"/>
       <c r="D26" s="37"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
@@ -1784,37 +1784,37 @@
       <c r="N26" s="24"/>
     </row>
     <row r="27" spans="1:14" ht="12.6" customHeight="1">
-      <c r="A27" s="116" t="s">
+      <c r="A27" s="81" t="s">
         <v>43</v>
       </c>
-      <c r="B27" s="109" t="s">
+      <c r="B27" s="87" t="s">
         <v>44</v>
       </c>
-      <c r="C27" s="109" t="s">
+      <c r="C27" s="87" t="s">
         <v>45</v>
       </c>
-      <c r="D27" s="110"/>
-      <c r="E27" s="109" t="s">
+      <c r="D27" s="88"/>
+      <c r="E27" s="87" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="110"/>
+      <c r="F27" s="88"/>
       <c r="G27" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="H27" s="86" t="s">
+      <c r="H27" s="121" t="s">
         <v>48</v>
       </c>
-      <c r="I27" s="87"/>
-      <c r="J27" s="114" t="s">
+      <c r="I27" s="80"/>
+      <c r="J27" s="105" t="s">
         <v>49</v>
       </c>
-      <c r="K27" s="91"/>
+      <c r="K27" s="97"/>
       <c r="L27" s="40"/>
       <c r="M27" s="40"/>
     </row>
     <row r="28" spans="1:14" ht="12.6" customHeight="1">
-      <c r="A28" s="117"/>
-      <c r="B28" s="113"/>
+      <c r="A28" s="82"/>
+      <c r="B28" s="104"/>
       <c r="C28" s="38" t="s">
         <v>50</v>
       </c>
@@ -1830,12 +1830,12 @@
       <c r="G28" s="41" t="s">
         <v>52</v>
       </c>
-      <c r="H28" s="84" t="s">
+      <c r="H28" s="120" t="s">
         <v>53</v>
       </c>
-      <c r="I28" s="83"/>
-      <c r="J28" s="96"/>
-      <c r="K28" s="97"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="98"/>
+      <c r="K28" s="94"/>
       <c r="L28" s="40"/>
       <c r="M28" s="40"/>
     </row>
@@ -2328,20 +2328,20 @@
     <row r="59" spans="1:17" ht="14.25" customHeight="1">
       <c r="A59" s="77"/>
       <c r="B59" s="10"/>
-      <c r="C59" s="122" t="s">
+      <c r="C59" s="107" t="s">
         <v>73</v>
       </c>
-      <c r="D59" s="122"/>
-      <c r="E59" s="122"/>
-      <c r="F59" s="122"/>
-      <c r="G59" s="122"/>
-      <c r="H59" s="122"/>
-      <c r="I59" s="122"/>
+      <c r="D59" s="107"/>
+      <c r="E59" s="107"/>
+      <c r="F59" s="107"/>
+      <c r="G59" s="107"/>
+      <c r="H59" s="107"/>
+      <c r="I59" s="107"/>
       <c r="K59" s="52"/>
-      <c r="N59" s="98"/>
-      <c r="O59" s="79"/>
-      <c r="P59" s="79"/>
-      <c r="Q59" s="79"/>
+      <c r="N59" s="108"/>
+      <c r="O59" s="102"/>
+      <c r="P59" s="102"/>
+      <c r="Q59" s="102"/>
     </row>
     <row r="60" spans="1:17" ht="12.75" customHeight="1">
       <c r="A60" s="58" t="s">
@@ -2444,40 +2444,40 @@
       <c r="N66" s="22"/>
     </row>
     <row r="67" spans="1:14" ht="12.6" customHeight="1">
-      <c r="A67" s="111" t="s">
+      <c r="A67" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="B67" s="112"/>
-      <c r="C67" s="112"/>
-      <c r="D67" s="119"/>
-      <c r="E67" s="112"/>
-      <c r="F67" s="112"/>
-      <c r="G67" s="112"/>
-      <c r="H67" s="112"/>
-      <c r="I67" s="112"/>
-      <c r="J67" s="100" t="s">
+      <c r="B67" s="86"/>
+      <c r="C67" s="86"/>
+      <c r="D67" s="85"/>
+      <c r="E67" s="86"/>
+      <c r="F67" s="86"/>
+      <c r="G67" s="86"/>
+      <c r="H67" s="86"/>
+      <c r="I67" s="86"/>
+      <c r="J67" s="110" t="s">
         <v>69</v>
       </c>
-      <c r="K67" s="101"/>
+      <c r="K67" s="111"/>
       <c r="L67" s="65"/>
       <c r="M67" s="65"/>
     </row>
     <row r="68" spans="1:14" ht="12.6" customHeight="1">
-      <c r="A68" s="115" t="s">
+      <c r="A68" s="106" t="s">
         <v>70</v>
       </c>
-      <c r="B68" s="79"/>
-      <c r="C68" s="79"/>
-      <c r="D68" s="108"/>
-      <c r="E68" s="79"/>
-      <c r="F68" s="79"/>
-      <c r="G68" s="79"/>
-      <c r="H68" s="79"/>
-      <c r="I68" s="79"/>
-      <c r="J68" s="107" t="s">
+      <c r="B68" s="102"/>
+      <c r="C68" s="102"/>
+      <c r="D68" s="101"/>
+      <c r="E68" s="102"/>
+      <c r="F68" s="102"/>
+      <c r="G68" s="102"/>
+      <c r="H68" s="102"/>
+      <c r="I68" s="102"/>
+      <c r="J68" s="99" t="s">
         <v>71</v>
       </c>
-      <c r="K68" s="95"/>
+      <c r="K68" s="100"/>
       <c r="L68" s="67"/>
       <c r="M68" s="67"/>
     </row>
@@ -2588,6 +2588,40 @@
     <row r="77" spans="1:14" ht="12.6" customHeight="1"/>
   </sheetData>
   <mergeCells count="50">
+    <mergeCell ref="A3:C4"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="D9:H9"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D8:H8"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="D17:K18"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D5:K5"/>
+    <mergeCell ref="D6:K6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="N59:Q59"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A8:C10"/>
+    <mergeCell ref="A12:C14"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="D11:H11"/>
+    <mergeCell ref="J68:K68"/>
+    <mergeCell ref="D68:I68"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="C59:I59"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A27:A28"/>
     <mergeCell ref="A16:B16"/>
@@ -2604,40 +2638,6 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="D14:K15"/>
-    <mergeCell ref="J68:K68"/>
-    <mergeCell ref="D68:I68"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="J27:K28"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="C59:I59"/>
-    <mergeCell ref="N59:Q59"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="J67:K67"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A8:C10"/>
-    <mergeCell ref="A12:C14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="D11:H11"/>
-    <mergeCell ref="A3:C4"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="D9:H9"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D8:H8"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="D17:K18"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D5:K5"/>
-    <mergeCell ref="D6:K6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="I7:K7"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.15763888888888899" right="0.15763888888888899" top="0.27569444444444402" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>
